--- a/SpaceDebris_site_1000/2008-048A_Ratsat_bolted_to_Falcon_1_Kestrel_upper_.xlsx
+++ b/SpaceDebris_site_1000/2008-048A_Ratsat_bolted_to_Falcon_1_Kestrel_upper_.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65.08</v>
+        <v>0.26</v>
       </c>
       <c r="B2" t="n">
-        <v>20589</v>
+        <v>37203</v>
       </c>
       <c r="C2" t="n">
-        <v>65.62</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>16626</v>
+        <v>27919</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105.81</v>
+        <v>0.87</v>
       </c>
       <c r="B3" t="n">
-        <v>45294</v>
+        <v>34660</v>
       </c>
       <c r="C3" t="n">
-        <v>106.56</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>15796</v>
+        <v>11840</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104.59</v>
+        <v>2.35</v>
       </c>
       <c r="B4" t="n">
-        <v>48163</v>
+        <v>34856</v>
       </c>
       <c r="C4" t="n">
-        <v>104.85</v>
+        <v>2.85</v>
       </c>
       <c r="D4" t="n">
-        <v>19322</v>
+        <v>11753</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112.78</v>
+        <v>2.36</v>
       </c>
       <c r="B5" t="n">
-        <v>27307</v>
+        <v>37738</v>
       </c>
       <c r="C5" t="n">
-        <v>108.97</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>14565</v>
+        <v>18375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102.89</v>
+        <v>2.39</v>
       </c>
       <c r="B6" t="n">
-        <v>46151</v>
+        <v>34601</v>
       </c>
       <c r="C6" t="n">
-        <v>102.8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>29117</v>
+        <v>11039</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93.48999999999999</v>
+        <v>2.68</v>
       </c>
       <c r="B7" t="n">
-        <v>28683</v>
+        <v>34987</v>
       </c>
       <c r="C7" t="n">
-        <v>91.38</v>
+        <v>4.6</v>
       </c>
       <c r="D7" t="n">
-        <v>19584</v>
+        <v>19621</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95.04000000000001</v>
+        <v>3.16</v>
       </c>
       <c r="B8" t="n">
-        <v>33850</v>
+        <v>36443</v>
       </c>
       <c r="C8" t="n">
-        <v>98.56</v>
+        <v>10.84</v>
       </c>
       <c r="D8" t="n">
-        <v>16983</v>
+        <v>27383</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91.29000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="B9" t="n">
-        <v>22554</v>
+        <v>36389</v>
       </c>
       <c r="C9" t="n">
-        <v>93.89</v>
+        <v>1.16</v>
       </c>
       <c r="D9" t="n">
-        <v>21565</v>
+        <v>10216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112.65</v>
+        <v>4.1</v>
       </c>
       <c r="B10" t="n">
-        <v>28444</v>
+        <v>33811</v>
       </c>
       <c r="C10" t="n">
-        <v>116.16</v>
+        <v>0.15</v>
       </c>
       <c r="D10" t="n">
-        <v>13567</v>
+        <v>11130</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103.95</v>
+        <v>5.35</v>
       </c>
       <c r="B11" t="n">
-        <v>47186</v>
+        <v>35828</v>
       </c>
       <c r="C11" t="n">
-        <v>107.57</v>
+        <v>13.76</v>
       </c>
       <c r="D11" t="n">
-        <v>24719</v>
+        <v>15657</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95.12</v>
+        <v>5.38</v>
       </c>
       <c r="B12" t="n">
-        <v>31922</v>
+        <v>33716</v>
       </c>
       <c r="C12" t="n">
-        <v>96.73999999999999</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>15593</v>
+        <v>11395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96.19</v>
+        <v>5.59</v>
       </c>
       <c r="B13" t="n">
-        <v>37443</v>
+        <v>34974</v>
       </c>
       <c r="C13" t="n">
-        <v>93.56999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="D13" t="n">
-        <v>19476</v>
+        <v>20825</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23.97</v>
+        <v>6.1</v>
       </c>
       <c r="B14" t="n">
-        <v>21259</v>
+        <v>34964</v>
       </c>
       <c r="C14" t="n">
-        <v>24.42</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>18929</v>
+        <v>14267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114.11</v>
+        <v>7.15</v>
       </c>
       <c r="B15" t="n">
-        <v>22105</v>
+        <v>33353</v>
       </c>
       <c r="C15" t="n">
-        <v>117.89</v>
+        <v>11.69</v>
       </c>
       <c r="D15" t="n">
-        <v>17583</v>
+        <v>23269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114.1</v>
+        <v>7.21</v>
       </c>
       <c r="B16" t="n">
-        <v>26641</v>
+        <v>33476</v>
       </c>
       <c r="C16" t="n">
-        <v>116.63</v>
+        <v>4.5</v>
       </c>
       <c r="D16" t="n">
-        <v>27275</v>
+        <v>21592</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108.04</v>
+        <v>7.3</v>
       </c>
       <c r="B17" t="n">
-        <v>38994</v>
+        <v>33458</v>
       </c>
       <c r="C17" t="n">
-        <v>111.52</v>
+        <v>2.9</v>
       </c>
       <c r="D17" t="n">
-        <v>26036</v>
+        <v>25781</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>91.93000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="B18" t="n">
-        <v>26910</v>
+        <v>31535</v>
       </c>
       <c r="C18" t="n">
-        <v>94.53</v>
+        <v>11.49</v>
       </c>
       <c r="D18" t="n">
-        <v>27142</v>
+        <v>27242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106.82</v>
+        <v>7.4</v>
       </c>
       <c r="B19" t="n">
-        <v>41716</v>
+        <v>31370</v>
       </c>
       <c r="C19" t="n">
-        <v>107.72</v>
+        <v>7.79</v>
       </c>
       <c r="D19" t="n">
-        <v>14892</v>
+        <v>23515</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97.62</v>
+        <v>7.84</v>
       </c>
       <c r="B20" t="n">
-        <v>42097</v>
+        <v>34225</v>
       </c>
       <c r="C20" t="n">
-        <v>95.5</v>
+        <v>11.68</v>
       </c>
       <c r="D20" t="n">
-        <v>28593</v>
+        <v>21495</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109.76</v>
+        <v>7.89</v>
       </c>
       <c r="B21" t="n">
-        <v>33240</v>
+        <v>33798</v>
       </c>
       <c r="C21" t="n">
-        <v>105.54</v>
+        <v>6.68</v>
       </c>
       <c r="D21" t="n">
-        <v>25743</v>
+        <v>24223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94.73999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="B22" t="n">
-        <v>31388</v>
+        <v>32660</v>
       </c>
       <c r="C22" t="n">
-        <v>97.58</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>11635</v>
+        <v>23432</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>90.40000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="B23" t="n">
-        <v>21291</v>
+        <v>32765</v>
       </c>
       <c r="C23" t="n">
-        <v>93.02</v>
+        <v>6.48</v>
       </c>
       <c r="D23" t="n">
-        <v>20958</v>
+        <v>16560</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>139.95</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="B24" t="n">
-        <v>22194</v>
+        <v>31288</v>
       </c>
       <c r="C24" t="n">
-        <v>136.04</v>
+        <v>3.8</v>
       </c>
       <c r="D24" t="n">
-        <v>17073</v>
+        <v>29747</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>78.34999999999999</v>
+        <v>10.19</v>
       </c>
       <c r="B25" t="n">
-        <v>25260</v>
+        <v>29190</v>
       </c>
       <c r="C25" t="n">
-        <v>79.14</v>
+        <v>14.37</v>
       </c>
       <c r="D25" t="n">
-        <v>24174</v>
+        <v>15392</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>50.72</v>
+        <v>10.44</v>
       </c>
       <c r="B26" t="n">
-        <v>24735</v>
+        <v>28670</v>
       </c>
       <c r="C26" t="n">
-        <v>50.13</v>
+        <v>17.12</v>
       </c>
       <c r="D26" t="n">
-        <v>23536</v>
+        <v>16567</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113.22</v>
+        <v>10.52</v>
       </c>
       <c r="B27" t="n">
-        <v>24943</v>
+        <v>29327</v>
       </c>
       <c r="C27" t="n">
-        <v>115.41</v>
+        <v>16.81</v>
       </c>
       <c r="D27" t="n">
-        <v>25796</v>
+        <v>22580</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107.11</v>
+        <v>10.55</v>
       </c>
       <c r="B28" t="n">
-        <v>40143</v>
+        <v>30548</v>
       </c>
       <c r="C28" t="n">
-        <v>103.86</v>
+        <v>23.87</v>
       </c>
       <c r="D28" t="n">
-        <v>16995</v>
+        <v>13632</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>98.84999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="B29" t="n">
-        <v>42909</v>
+        <v>31369</v>
       </c>
       <c r="C29" t="n">
-        <v>97.22</v>
+        <v>12.7</v>
       </c>
       <c r="D29" t="n">
-        <v>26723</v>
+        <v>29725</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112.97</v>
+        <v>12.62</v>
       </c>
       <c r="B30" t="n">
-        <v>26866</v>
+        <v>28355</v>
       </c>
       <c r="C30" t="n">
-        <v>113.83</v>
+        <v>21.26</v>
       </c>
       <c r="D30" t="n">
-        <v>22686</v>
+        <v>10169</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>94.53</v>
+        <v>13.03</v>
       </c>
       <c r="B31" t="n">
-        <v>30190</v>
+        <v>27436</v>
       </c>
       <c r="C31" t="n">
-        <v>98.33</v>
+        <v>15.3</v>
       </c>
       <c r="D31" t="n">
-        <v>24909</v>
+        <v>11026</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>99.36</v>
+        <v>13.04</v>
       </c>
       <c r="B32" t="n">
-        <v>41768</v>
+        <v>29447</v>
       </c>
       <c r="C32" t="n">
-        <v>102.08</v>
+        <v>5.56</v>
       </c>
       <c r="D32" t="n">
-        <v>18421</v>
+        <v>27180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>57.22</v>
+        <v>13.09</v>
       </c>
       <c r="B33" t="n">
-        <v>23446</v>
+        <v>26096</v>
       </c>
       <c r="C33" t="n">
-        <v>58.64</v>
+        <v>20.21</v>
       </c>
       <c r="D33" t="n">
-        <v>14578</v>
+        <v>19508</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>107.59</v>
+        <v>13.42</v>
       </c>
       <c r="B34" t="n">
-        <v>37285</v>
+        <v>27869</v>
       </c>
       <c r="C34" t="n">
-        <v>106.82</v>
+        <v>14.27</v>
       </c>
       <c r="D34" t="n">
-        <v>10473</v>
+        <v>27653</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>100.36</v>
+        <v>13.8</v>
       </c>
       <c r="B35" t="n">
-        <v>44030</v>
+        <v>28150</v>
       </c>
       <c r="C35" t="n">
-        <v>102.93</v>
+        <v>13.39</v>
       </c>
       <c r="D35" t="n">
-        <v>19728</v>
+        <v>14555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111.56</v>
+        <v>14.4</v>
       </c>
       <c r="B36" t="n">
-        <v>27590</v>
+        <v>26696</v>
       </c>
       <c r="C36" t="n">
-        <v>115.15</v>
+        <v>6.44</v>
       </c>
       <c r="D36" t="n">
-        <v>12636</v>
+        <v>20133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>94.89</v>
+        <v>14.4</v>
       </c>
       <c r="B37" t="n">
-        <v>31316</v>
+        <v>25625</v>
       </c>
       <c r="C37" t="n">
-        <v>93.93000000000001</v>
+        <v>14.15</v>
       </c>
       <c r="D37" t="n">
-        <v>28729</v>
+        <v>29001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>43.18</v>
+        <v>14.56</v>
       </c>
       <c r="B38" t="n">
-        <v>25530</v>
+        <v>25537</v>
       </c>
       <c r="C38" t="n">
-        <v>41.85</v>
+        <v>16.49</v>
       </c>
       <c r="D38" t="n">
-        <v>25477</v>
+        <v>20638</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>76.28</v>
+        <v>14.92</v>
       </c>
       <c r="B39" t="n">
-        <v>23744</v>
+        <v>25309</v>
       </c>
       <c r="C39" t="n">
-        <v>77.84999999999999</v>
+        <v>15.98</v>
       </c>
       <c r="D39" t="n">
-        <v>15657</v>
+        <v>22754</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>97.29000000000001</v>
+        <v>15.23</v>
       </c>
       <c r="B40" t="n">
-        <v>36939</v>
+        <v>26362</v>
       </c>
       <c r="C40" t="n">
-        <v>100.8</v>
+        <v>13.21</v>
       </c>
       <c r="D40" t="n">
-        <v>15491</v>
+        <v>19601</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104.58</v>
+        <v>15.58</v>
       </c>
       <c r="B41" t="n">
-        <v>44591</v>
+        <v>28518</v>
       </c>
       <c r="C41" t="n">
-        <v>108.16</v>
+        <v>26.21</v>
       </c>
       <c r="D41" t="n">
-        <v>17399</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>94.81</v>
+        <v>16.67</v>
       </c>
       <c r="B42" t="n">
-        <v>33268</v>
+        <v>24046</v>
       </c>
       <c r="C42" t="n">
-        <v>96.65000000000001</v>
+        <v>24.83</v>
       </c>
       <c r="D42" t="n">
-        <v>24979</v>
+        <v>11953</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96.59</v>
+        <v>16.98</v>
       </c>
       <c r="B43" t="n">
-        <v>38099</v>
+        <v>23810</v>
       </c>
       <c r="C43" t="n">
-        <v>98.26000000000001</v>
+        <v>13.88</v>
       </c>
       <c r="D43" t="n">
-        <v>19560</v>
+        <v>14080</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8.109999999999999</v>
+        <v>17.22</v>
       </c>
       <c r="B44" t="n">
-        <v>23731</v>
+        <v>22954</v>
       </c>
       <c r="C44" t="n">
-        <v>7.99</v>
+        <v>4.86</v>
       </c>
       <c r="D44" t="n">
-        <v>28120</v>
+        <v>13556</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>82.68000000000001</v>
+        <v>17.45</v>
       </c>
       <c r="B45" t="n">
-        <v>24967</v>
+        <v>26144</v>
       </c>
       <c r="C45" t="n">
-        <v>85.89</v>
+        <v>22.01</v>
       </c>
       <c r="D45" t="n">
-        <v>21245</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>98.58</v>
+        <v>17.68</v>
       </c>
       <c r="B46" t="n">
-        <v>41117</v>
+        <v>23890</v>
       </c>
       <c r="C46" t="n">
-        <v>96.72</v>
+        <v>10.46</v>
       </c>
       <c r="D46" t="n">
-        <v>14534</v>
+        <v>28696</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131.19</v>
+        <v>17.98</v>
       </c>
       <c r="B47" t="n">
-        <v>22309</v>
+        <v>24692</v>
       </c>
       <c r="C47" t="n">
-        <v>129.15</v>
+        <v>17.47</v>
       </c>
       <c r="D47" t="n">
-        <v>25743</v>
+        <v>29532</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>102.23</v>
+        <v>18.09</v>
       </c>
       <c r="B48" t="n">
-        <v>45689</v>
+        <v>21679</v>
       </c>
       <c r="C48" t="n">
-        <v>104.69</v>
+        <v>12.06</v>
       </c>
       <c r="D48" t="n">
-        <v>28761</v>
+        <v>19350</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>52.42</v>
+        <v>18.31</v>
       </c>
       <c r="B49" t="n">
-        <v>24305</v>
+        <v>24020</v>
       </c>
       <c r="C49" t="n">
-        <v>51.89</v>
+        <v>18.7</v>
       </c>
       <c r="D49" t="n">
-        <v>24023</v>
+        <v>24246</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>102.54</v>
+        <v>19.26</v>
       </c>
       <c r="B50" t="n">
-        <v>46491</v>
+        <v>24613</v>
       </c>
       <c r="C50" t="n">
-        <v>100.6</v>
+        <v>21.06</v>
       </c>
       <c r="D50" t="n">
-        <v>16880</v>
+        <v>25664</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>107.19</v>
+        <v>19.69</v>
       </c>
       <c r="B51" t="n">
-        <v>39723</v>
+        <v>25513</v>
       </c>
       <c r="C51" t="n">
-        <v>111.03</v>
+        <v>18.03</v>
       </c>
       <c r="D51" t="n">
-        <v>25754</v>
+        <v>18869</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>92.34999999999999</v>
+        <v>19.81</v>
       </c>
       <c r="B52" t="n">
-        <v>27740</v>
+        <v>22967</v>
       </c>
       <c r="C52" t="n">
-        <v>90.06999999999999</v>
+        <v>15.83</v>
       </c>
       <c r="D52" t="n">
-        <v>27374</v>
+        <v>22767</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102.36</v>
+        <v>20.46</v>
       </c>
       <c r="B53" t="n">
-        <v>47236</v>
+        <v>23348</v>
       </c>
       <c r="C53" t="n">
-        <v>105.92</v>
+        <v>22.94</v>
       </c>
       <c r="D53" t="n">
-        <v>12663</v>
+        <v>21183</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114.78</v>
+        <v>20.84</v>
       </c>
       <c r="B54" t="n">
-        <v>24802</v>
+        <v>23763</v>
       </c>
       <c r="C54" t="n">
-        <v>115.57</v>
+        <v>18.74</v>
       </c>
       <c r="D54" t="n">
-        <v>27853</v>
+        <v>26669</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111.36</v>
+        <v>20.98</v>
       </c>
       <c r="B55" t="n">
-        <v>27331</v>
+        <v>23486</v>
       </c>
       <c r="C55" t="n">
-        <v>114.15</v>
+        <v>26.47</v>
       </c>
       <c r="D55" t="n">
-        <v>27738</v>
+        <v>29591</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>94.92</v>
+        <v>21.06</v>
       </c>
       <c r="B56" t="n">
-        <v>32991</v>
+        <v>23660</v>
       </c>
       <c r="C56" t="n">
-        <v>95.5</v>
+        <v>21.27</v>
       </c>
       <c r="D56" t="n">
-        <v>26612</v>
+        <v>11910</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104.03</v>
+        <v>21.15</v>
       </c>
       <c r="B57" t="n">
-        <v>46985</v>
+        <v>24093</v>
       </c>
       <c r="C57" t="n">
-        <v>103.3</v>
+        <v>24.66</v>
       </c>
       <c r="D57" t="n">
-        <v>17857</v>
+        <v>20696</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>107.94</v>
+        <v>21.99</v>
       </c>
       <c r="B58" t="n">
-        <v>38974</v>
+        <v>22270</v>
       </c>
       <c r="C58" t="n">
-        <v>105.24</v>
+        <v>17.37</v>
       </c>
       <c r="D58" t="n">
-        <v>21638</v>
+        <v>26438</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>95.69</v>
+        <v>22.83</v>
       </c>
       <c r="B59" t="n">
-        <v>36072</v>
+        <v>21620</v>
       </c>
       <c r="C59" t="n">
-        <v>92.36</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>19982</v>
+        <v>13701</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>152.53</v>
+        <v>23.42</v>
       </c>
       <c r="B60" t="n">
-        <v>23363</v>
+        <v>22893</v>
       </c>
       <c r="C60" t="n">
-        <v>155.78</v>
+        <v>18.67</v>
       </c>
       <c r="D60" t="n">
-        <v>23013</v>
+        <v>16080</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>94.11</v>
+        <v>23.54</v>
       </c>
       <c r="B61" t="n">
-        <v>31300</v>
+        <v>22642</v>
       </c>
       <c r="C61" t="n">
-        <v>91.15000000000001</v>
+        <v>25.9</v>
       </c>
       <c r="D61" t="n">
-        <v>28570</v>
+        <v>16768</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>109.06</v>
+        <v>23.68</v>
       </c>
       <c r="B62" t="n">
-        <v>35845</v>
+        <v>21765</v>
       </c>
       <c r="C62" t="n">
-        <v>103.77</v>
+        <v>28.22</v>
       </c>
       <c r="D62" t="n">
-        <v>11713</v>
+        <v>14218</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>101.67</v>
+        <v>24.1</v>
       </c>
       <c r="B63" t="n">
-        <v>47737</v>
+        <v>22755</v>
       </c>
       <c r="C63" t="n">
-        <v>99.58</v>
+        <v>23.37</v>
       </c>
       <c r="D63" t="n">
-        <v>14430</v>
+        <v>19406</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>93.37</v>
+        <v>24.42</v>
       </c>
       <c r="B64" t="n">
-        <v>29330</v>
+        <v>21871</v>
       </c>
       <c r="C64" t="n">
-        <v>96.19</v>
+        <v>23.85</v>
       </c>
       <c r="D64" t="n">
-        <v>19777</v>
+        <v>13709</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>100.26</v>
+        <v>24.94</v>
       </c>
       <c r="B65" t="n">
-        <v>44974</v>
+        <v>20821</v>
       </c>
       <c r="C65" t="n">
-        <v>103.69</v>
+        <v>24.7</v>
       </c>
       <c r="D65" t="n">
-        <v>24832</v>
+        <v>22883</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>98.20999999999999</v>
+        <v>25.23</v>
       </c>
       <c r="B66" t="n">
-        <v>42316</v>
+        <v>21594</v>
       </c>
       <c r="C66" t="n">
-        <v>98.13</v>
+        <v>31.59</v>
       </c>
       <c r="D66" t="n">
-        <v>28734</v>
+        <v>26490</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>101.73</v>
+        <v>25.68</v>
       </c>
       <c r="B67" t="n">
-        <v>43555</v>
+        <v>19717</v>
       </c>
       <c r="C67" t="n">
-        <v>100.47</v>
+        <v>18.49</v>
       </c>
       <c r="D67" t="n">
-        <v>29196</v>
+        <v>16007</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>98.56999999999999</v>
+        <v>25.99</v>
       </c>
       <c r="B68" t="n">
-        <v>42540</v>
+        <v>21471</v>
       </c>
       <c r="C68" t="n">
-        <v>96.33</v>
+        <v>13.57</v>
       </c>
       <c r="D68" t="n">
-        <v>12199</v>
+        <v>27950</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>99.19</v>
+        <v>26.24</v>
       </c>
       <c r="B69" t="n">
-        <v>46125</v>
+        <v>20878</v>
       </c>
       <c r="C69" t="n">
-        <v>100.81</v>
+        <v>15.05</v>
       </c>
       <c r="D69" t="n">
-        <v>17822</v>
+        <v>26860</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>103.27</v>
+        <v>27.62</v>
       </c>
       <c r="B70" t="n">
-        <v>46851</v>
+        <v>22184</v>
       </c>
       <c r="C70" t="n">
-        <v>99.59999999999999</v>
+        <v>27.01</v>
       </c>
       <c r="D70" t="n">
-        <v>21067</v>
+        <v>24798</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>64.05</v>
+        <v>27.62</v>
       </c>
       <c r="B71" t="n">
-        <v>25127</v>
+        <v>22310</v>
       </c>
       <c r="C71" t="n">
-        <v>66.18000000000001</v>
+        <v>21.89</v>
       </c>
       <c r="D71" t="n">
-        <v>16154</v>
+        <v>23415</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>90.3</v>
+        <v>27.78</v>
       </c>
       <c r="B72" t="n">
-        <v>21144</v>
+        <v>20698</v>
       </c>
       <c r="C72" t="n">
-        <v>88.84999999999999</v>
+        <v>19.78</v>
       </c>
       <c r="D72" t="n">
-        <v>25347</v>
+        <v>29319</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>101.27</v>
+        <v>28.43</v>
       </c>
       <c r="B73" t="n">
-        <v>45255</v>
+        <v>21032</v>
       </c>
       <c r="C73" t="n">
-        <v>102.76</v>
+        <v>30.42</v>
       </c>
       <c r="D73" t="n">
-        <v>16292</v>
+        <v>23425</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102.94</v>
+        <v>28.71</v>
       </c>
       <c r="B74" t="n">
-        <v>46428</v>
+        <v>21803</v>
       </c>
       <c r="C74" t="n">
-        <v>106.65</v>
+        <v>25.29</v>
       </c>
       <c r="D74" t="n">
-        <v>13109</v>
+        <v>19612</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>111.21</v>
+        <v>29.66</v>
       </c>
       <c r="B75" t="n">
-        <v>27250</v>
+        <v>21309</v>
       </c>
       <c r="C75" t="n">
-        <v>115.13</v>
+        <v>27.9</v>
       </c>
       <c r="D75" t="n">
-        <v>18016</v>
+        <v>15334</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>100.96</v>
+        <v>29.67</v>
       </c>
       <c r="B76" t="n">
-        <v>44413</v>
+        <v>19311</v>
       </c>
       <c r="C76" t="n">
-        <v>105.17</v>
+        <v>23.23</v>
       </c>
       <c r="D76" t="n">
-        <v>16072</v>
+        <v>28141</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>90.17</v>
+        <v>29.9</v>
       </c>
       <c r="B77" t="n">
-        <v>24049</v>
+        <v>19396</v>
       </c>
       <c r="C77" t="n">
-        <v>87.92</v>
+        <v>31.98</v>
       </c>
       <c r="D77" t="n">
-        <v>12245</v>
+        <v>14696</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104.64</v>
+        <v>30.05</v>
       </c>
       <c r="B78" t="n">
-        <v>44792</v>
+        <v>21323</v>
       </c>
       <c r="C78" t="n">
-        <v>107.01</v>
+        <v>33.66</v>
       </c>
       <c r="D78" t="n">
-        <v>15960</v>
+        <v>18274</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>138.09</v>
+        <v>31.42</v>
       </c>
       <c r="B79" t="n">
-        <v>26276</v>
+        <v>23741</v>
       </c>
       <c r="C79" t="n">
-        <v>133.38</v>
+        <v>27.08</v>
       </c>
       <c r="D79" t="n">
-        <v>17537</v>
+        <v>12635</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>107.7</v>
+        <v>31.71</v>
       </c>
       <c r="B80" t="n">
-        <v>40062</v>
+        <v>21993</v>
       </c>
       <c r="C80" t="n">
-        <v>110.62</v>
+        <v>44.05</v>
       </c>
       <c r="D80" t="n">
-        <v>20083</v>
+        <v>16887</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>104.87</v>
+        <v>31.8</v>
       </c>
       <c r="B81" t="n">
-        <v>45101</v>
+        <v>22268</v>
       </c>
       <c r="C81" t="n">
-        <v>103.68</v>
+        <v>29.41</v>
       </c>
       <c r="D81" t="n">
-        <v>28927</v>
+        <v>13561</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112.63</v>
+        <v>32.17</v>
       </c>
       <c r="B82" t="n">
-        <v>25980</v>
+        <v>20845</v>
       </c>
       <c r="C82" t="n">
-        <v>112.31</v>
+        <v>26.03</v>
       </c>
       <c r="D82" t="n">
-        <v>22100</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134.33</v>
+        <v>32.37</v>
       </c>
       <c r="B83" t="n">
-        <v>24308</v>
+        <v>19992</v>
       </c>
       <c r="C83" t="n">
-        <v>134.13</v>
+        <v>41.91</v>
       </c>
       <c r="D83" t="n">
-        <v>16761</v>
+        <v>28801</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>92.59999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="B84" t="n">
-        <v>26875</v>
+        <v>23331</v>
       </c>
       <c r="C84" t="n">
-        <v>91.84999999999999</v>
+        <v>30.16</v>
       </c>
       <c r="D84" t="n">
-        <v>19160</v>
+        <v>23284</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>88.2</v>
+        <v>32.83</v>
       </c>
       <c r="B85" t="n">
-        <v>23338</v>
+        <v>22806</v>
       </c>
       <c r="C85" t="n">
-        <v>88.26000000000001</v>
+        <v>33.45</v>
       </c>
       <c r="D85" t="n">
-        <v>16875</v>
+        <v>12882</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>106.22</v>
+        <v>34.24</v>
       </c>
       <c r="B86" t="n">
-        <v>44821</v>
+        <v>23526</v>
       </c>
       <c r="C86" t="n">
-        <v>105.33</v>
+        <v>48.58</v>
       </c>
       <c r="D86" t="n">
-        <v>27521</v>
+        <v>20673</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>103.24</v>
+        <v>34.84</v>
       </c>
       <c r="B87" t="n">
-        <v>49076</v>
+        <v>21342</v>
       </c>
       <c r="C87" t="n">
-        <v>103.54</v>
+        <v>28.32</v>
       </c>
       <c r="D87" t="n">
-        <v>25964</v>
+        <v>17964</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>90.59</v>
+        <v>35.14</v>
       </c>
       <c r="B88" t="n">
-        <v>24847</v>
+        <v>23676</v>
       </c>
       <c r="C88" t="n">
-        <v>94.2</v>
+        <v>28.4</v>
       </c>
       <c r="D88" t="n">
-        <v>24268</v>
+        <v>22619</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>97.09</v>
+        <v>35.99</v>
       </c>
       <c r="B89" t="n">
-        <v>38089</v>
+        <v>22140</v>
       </c>
       <c r="C89" t="n">
-        <v>97.06999999999999</v>
+        <v>41.37</v>
       </c>
       <c r="D89" t="n">
-        <v>26896</v>
+        <v>23537</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>66.7</v>
+        <v>36.74</v>
       </c>
       <c r="B90" t="n">
-        <v>28145</v>
+        <v>19605</v>
       </c>
       <c r="C90" t="n">
-        <v>67.34</v>
+        <v>37.97</v>
       </c>
       <c r="D90" t="n">
-        <v>17061</v>
+        <v>25230</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>99.83</v>
+        <v>37.69</v>
       </c>
       <c r="B91" t="n">
-        <v>45164</v>
+        <v>22396</v>
       </c>
       <c r="C91" t="n">
-        <v>97.98</v>
+        <v>42.61</v>
       </c>
       <c r="D91" t="n">
-        <v>22957</v>
+        <v>26721</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112.67</v>
+        <v>38.5</v>
       </c>
       <c r="B92" t="n">
-        <v>26426</v>
+        <v>23292</v>
       </c>
       <c r="C92" t="n">
-        <v>110.51</v>
+        <v>51.51</v>
       </c>
       <c r="D92" t="n">
-        <v>19048</v>
+        <v>15436</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>93.09999999999999</v>
+        <v>38.6</v>
       </c>
       <c r="B93" t="n">
-        <v>29998</v>
+        <v>22137</v>
       </c>
       <c r="C93" t="n">
-        <v>95.66</v>
+        <v>34.96</v>
       </c>
       <c r="D93" t="n">
-        <v>21110</v>
+        <v>23394</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>114.05</v>
+        <v>38.73</v>
       </c>
       <c r="B94" t="n">
-        <v>23668</v>
+        <v>22261</v>
       </c>
       <c r="C94" t="n">
-        <v>110.4</v>
+        <v>31.48</v>
       </c>
       <c r="D94" t="n">
-        <v>11667</v>
+        <v>25257</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>151.84</v>
+        <v>38.74</v>
       </c>
       <c r="B95" t="n">
-        <v>23364</v>
+        <v>20105</v>
       </c>
       <c r="C95" t="n">
-        <v>152.99</v>
+        <v>37.95</v>
       </c>
       <c r="D95" t="n">
-        <v>21989</v>
+        <v>20987</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>90.98</v>
+        <v>38.96</v>
       </c>
       <c r="B96" t="n">
-        <v>27640</v>
+        <v>20861</v>
       </c>
       <c r="C96" t="n">
-        <v>89.06</v>
+        <v>47.32</v>
       </c>
       <c r="D96" t="n">
-        <v>16267</v>
+        <v>26451</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>109.45</v>
+        <v>38.97</v>
       </c>
       <c r="B97" t="n">
-        <v>31672</v>
+        <v>20963</v>
       </c>
       <c r="C97" t="n">
-        <v>106.79</v>
+        <v>26.46</v>
       </c>
       <c r="D97" t="n">
-        <v>22732</v>
+        <v>19315</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97.68000000000001</v>
+        <v>39.07</v>
       </c>
       <c r="B98" t="n">
-        <v>39639</v>
+        <v>21137</v>
       </c>
       <c r="C98" t="n">
-        <v>96.12</v>
+        <v>37.77</v>
       </c>
       <c r="D98" t="n">
-        <v>20621</v>
+        <v>11821</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>109.41</v>
+        <v>39.14</v>
       </c>
       <c r="B99" t="n">
-        <v>35112</v>
+        <v>20361</v>
       </c>
       <c r="C99" t="n">
-        <v>106.61</v>
+        <v>44.57</v>
       </c>
       <c r="D99" t="n">
-        <v>26568</v>
+        <v>13475</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>108.43</v>
+        <v>39.31</v>
       </c>
       <c r="B100" t="n">
-        <v>36560</v>
+        <v>20171</v>
       </c>
       <c r="C100" t="n">
-        <v>112.08</v>
+        <v>51.83</v>
       </c>
       <c r="D100" t="n">
-        <v>27434</v>
+        <v>15109</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>104.82</v>
+        <v>39.82</v>
       </c>
       <c r="B101" t="n">
-        <v>46333</v>
+        <v>19825</v>
       </c>
       <c r="C101" t="n">
-        <v>102.04</v>
+        <v>28.92</v>
       </c>
       <c r="D101" t="n">
-        <v>26965</v>
+        <v>13760</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>98.2</v>
+        <v>39.93</v>
       </c>
       <c r="B102" t="n">
-        <v>43228</v>
+        <v>22064</v>
       </c>
       <c r="C102" t="n">
-        <v>95.5</v>
+        <v>31.54</v>
       </c>
       <c r="D102" t="n">
-        <v>18218</v>
+        <v>21244</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>62.71</v>
+        <v>40.03</v>
       </c>
       <c r="B103" t="n">
-        <v>23469</v>
+        <v>21441</v>
       </c>
       <c r="C103" t="n">
-        <v>63.5</v>
+        <v>44.49</v>
       </c>
       <c r="D103" t="n">
-        <v>24636</v>
+        <v>18502</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>139.69</v>
+        <v>40.65</v>
       </c>
       <c r="B104" t="n">
-        <v>22638</v>
+        <v>23779</v>
       </c>
       <c r="C104" t="n">
-        <v>139.94</v>
+        <v>40.63</v>
       </c>
       <c r="D104" t="n">
-        <v>19506</v>
+        <v>10277</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>101.36</v>
+        <v>40.87</v>
       </c>
       <c r="B105" t="n">
-        <v>46623</v>
+        <v>21894</v>
       </c>
       <c r="C105" t="n">
-        <v>102.61</v>
+        <v>47.07</v>
       </c>
       <c r="D105" t="n">
-        <v>24331</v>
+        <v>15319</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>90.45999999999999</v>
+        <v>41.27</v>
       </c>
       <c r="B106" t="n">
-        <v>21422</v>
+        <v>22116</v>
       </c>
       <c r="C106" t="n">
-        <v>93.41</v>
+        <v>33.15</v>
       </c>
       <c r="D106" t="n">
-        <v>15280</v>
+        <v>11251</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>106.07</v>
+        <v>41.45</v>
       </c>
       <c r="B107" t="n">
-        <v>43971</v>
+        <v>20134</v>
       </c>
       <c r="C107" t="n">
-        <v>102.93</v>
+        <v>34.62</v>
       </c>
       <c r="D107" t="n">
-        <v>19194</v>
+        <v>29696</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>104.1</v>
+        <v>41.5</v>
       </c>
       <c r="B108" t="n">
-        <v>47000</v>
+        <v>20196</v>
       </c>
       <c r="C108" t="n">
-        <v>106.17</v>
+        <v>37.08</v>
       </c>
       <c r="D108" t="n">
-        <v>13665</v>
+        <v>25195</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112.21</v>
+        <v>41.52</v>
       </c>
       <c r="B109" t="n">
-        <v>25250</v>
+        <v>25082</v>
       </c>
       <c r="C109" t="n">
-        <v>113.71</v>
+        <v>37.24</v>
       </c>
       <c r="D109" t="n">
-        <v>25453</v>
+        <v>16852</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>92.45999999999999</v>
+        <v>42.24</v>
       </c>
       <c r="B110" t="n">
-        <v>27842</v>
+        <v>19939</v>
       </c>
       <c r="C110" t="n">
-        <v>95.19</v>
+        <v>47.13</v>
       </c>
       <c r="D110" t="n">
-        <v>22087</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>167.63</v>
+        <v>42.29</v>
       </c>
       <c r="B111" t="n">
-        <v>23436</v>
+        <v>21329</v>
       </c>
       <c r="C111" t="n">
-        <v>162.41</v>
+        <v>32.14</v>
       </c>
       <c r="D111" t="n">
-        <v>18099</v>
+        <v>14538</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>106.07</v>
+        <v>42.32</v>
       </c>
       <c r="B112" t="n">
-        <v>45104</v>
+        <v>19054</v>
       </c>
       <c r="C112" t="n">
-        <v>102.41</v>
+        <v>47.7</v>
       </c>
       <c r="D112" t="n">
-        <v>15005</v>
+        <v>15680</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>107.16</v>
+        <v>43.41</v>
       </c>
       <c r="B113" t="n">
-        <v>42040</v>
+        <v>23461</v>
       </c>
       <c r="C113" t="n">
-        <v>107.81</v>
+        <v>53.89</v>
       </c>
       <c r="D113" t="n">
-        <v>18103</v>
+        <v>10220</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>96.66</v>
+        <v>44.59</v>
       </c>
       <c r="B114" t="n">
-        <v>37681</v>
+        <v>23850</v>
       </c>
       <c r="C114" t="n">
-        <v>94.14</v>
+        <v>49.54</v>
       </c>
       <c r="D114" t="n">
-        <v>29011</v>
+        <v>25786</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>94.77</v>
+        <v>44.73</v>
       </c>
       <c r="B115" t="n">
-        <v>33011</v>
+        <v>22155</v>
       </c>
       <c r="C115" t="n">
-        <v>96.41</v>
+        <v>43.37</v>
       </c>
       <c r="D115" t="n">
-        <v>18385</v>
+        <v>19201</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>110.38</v>
+        <v>44.77</v>
       </c>
       <c r="B116" t="n">
-        <v>29469</v>
+        <v>18972</v>
       </c>
       <c r="C116" t="n">
-        <v>108.21</v>
+        <v>35.05</v>
       </c>
       <c r="D116" t="n">
-        <v>12206</v>
+        <v>26450</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>101</v>
+        <v>45.04</v>
       </c>
       <c r="B117" t="n">
-        <v>44897</v>
+        <v>20795</v>
       </c>
       <c r="C117" t="n">
-        <v>102.04</v>
+        <v>44.28</v>
       </c>
       <c r="D117" t="n">
-        <v>10030</v>
+        <v>12843</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>85.54000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="B118" t="n">
-        <v>24324</v>
+        <v>21425</v>
       </c>
       <c r="C118" t="n">
-        <v>88.44</v>
+        <v>42.94</v>
       </c>
       <c r="D118" t="n">
-        <v>24471</v>
+        <v>28103</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121.35</v>
+        <v>45.23</v>
       </c>
       <c r="B119" t="n">
-        <v>24113</v>
+        <v>20977</v>
       </c>
       <c r="C119" t="n">
-        <v>124.45</v>
+        <v>40.46</v>
       </c>
       <c r="D119" t="n">
-        <v>11214</v>
+        <v>15828</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>100.88</v>
+        <v>47.16</v>
       </c>
       <c r="B120" t="n">
-        <v>41756</v>
+        <v>21999</v>
       </c>
       <c r="C120" t="n">
-        <v>102.31</v>
+        <v>45.52</v>
       </c>
       <c r="D120" t="n">
-        <v>22041</v>
+        <v>14825</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>106.8</v>
+        <v>47.36</v>
       </c>
       <c r="B121" t="n">
-        <v>42566</v>
+        <v>19054</v>
       </c>
       <c r="C121" t="n">
-        <v>110.09</v>
+        <v>39.3</v>
       </c>
       <c r="D121" t="n">
-        <v>13546</v>
+        <v>27521</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>92.02</v>
+        <v>47.61</v>
       </c>
       <c r="B122" t="n">
-        <v>26160</v>
+        <v>19929</v>
       </c>
       <c r="C122" t="n">
-        <v>95.2</v>
+        <v>41.52</v>
       </c>
       <c r="D122" t="n">
-        <v>17163</v>
+        <v>15045</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>94.58</v>
+        <v>48.05</v>
       </c>
       <c r="B123" t="n">
-        <v>33373</v>
+        <v>20041</v>
       </c>
       <c r="C123" t="n">
-        <v>92.48</v>
+        <v>53.97</v>
       </c>
       <c r="D123" t="n">
-        <v>25548</v>
+        <v>23088</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>109.54</v>
+        <v>48.48</v>
       </c>
       <c r="B124" t="n">
-        <v>33849</v>
+        <v>20410</v>
       </c>
       <c r="C124" t="n">
-        <v>107.72</v>
+        <v>35.38</v>
       </c>
       <c r="D124" t="n">
-        <v>26899</v>
+        <v>26552</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>100.96</v>
+        <v>48.62</v>
       </c>
       <c r="B125" t="n">
-        <v>46600</v>
+        <v>22006</v>
       </c>
       <c r="C125" t="n">
-        <v>100.46</v>
+        <v>51.17</v>
       </c>
       <c r="D125" t="n">
-        <v>13435</v>
+        <v>29323</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>95.33</v>
+        <v>49.65</v>
       </c>
       <c r="B126" t="n">
-        <v>34347</v>
+        <v>20958</v>
       </c>
       <c r="C126" t="n">
-        <v>92.45</v>
+        <v>43.93</v>
       </c>
       <c r="D126" t="n">
-        <v>17995</v>
+        <v>20664</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>114.27</v>
+        <v>49.74</v>
       </c>
       <c r="B127" t="n">
-        <v>24796</v>
+        <v>19280</v>
       </c>
       <c r="C127" t="n">
-        <v>111.01</v>
+        <v>47.63</v>
       </c>
       <c r="D127" t="n">
-        <v>20869</v>
+        <v>13944</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>107.28</v>
+        <v>50.11</v>
       </c>
       <c r="B128" t="n">
-        <v>41865</v>
+        <v>20937</v>
       </c>
       <c r="C128" t="n">
-        <v>108.14</v>
+        <v>60.38</v>
       </c>
       <c r="D128" t="n">
-        <v>12301</v>
+        <v>15561</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>92.48</v>
+        <v>50.41</v>
       </c>
       <c r="B129" t="n">
-        <v>27122</v>
+        <v>19412</v>
       </c>
       <c r="C129" t="n">
-        <v>89.91</v>
+        <v>54.27</v>
       </c>
       <c r="D129" t="n">
-        <v>17718</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132.84</v>
+        <v>50.44</v>
       </c>
       <c r="B130" t="n">
-        <v>21027</v>
+        <v>19390</v>
       </c>
       <c r="C130" t="n">
-        <v>129.58</v>
+        <v>51.54</v>
       </c>
       <c r="D130" t="n">
-        <v>29175</v>
+        <v>15294</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>96.59</v>
+        <v>50.53</v>
       </c>
       <c r="B131" t="n">
-        <v>40886</v>
+        <v>20189</v>
       </c>
       <c r="C131" t="n">
-        <v>97.93000000000001</v>
+        <v>44.64</v>
       </c>
       <c r="D131" t="n">
-        <v>16038</v>
+        <v>10367</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>168.43</v>
+        <v>50.84</v>
       </c>
       <c r="B132" t="n">
-        <v>22010</v>
+        <v>19715</v>
       </c>
       <c r="C132" t="n">
-        <v>168.1</v>
+        <v>40.25</v>
       </c>
       <c r="D132" t="n">
-        <v>27962</v>
+        <v>21994</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>91.5</v>
+        <v>50.99</v>
       </c>
       <c r="B133" t="n">
-        <v>23055</v>
+        <v>23272</v>
       </c>
       <c r="C133" t="n">
-        <v>93.12</v>
+        <v>35.7</v>
       </c>
       <c r="D133" t="n">
-        <v>15203</v>
+        <v>19444</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>91.55</v>
+        <v>51.08</v>
       </c>
       <c r="B134" t="n">
-        <v>27483</v>
+        <v>23314</v>
       </c>
       <c r="C134" t="n">
-        <v>89.16</v>
+        <v>42.94</v>
       </c>
       <c r="D134" t="n">
-        <v>22893</v>
+        <v>12696</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>91.59</v>
+        <v>51.32</v>
       </c>
       <c r="B135" t="n">
-        <v>23421</v>
+        <v>19609</v>
       </c>
       <c r="C135" t="n">
-        <v>93.09999999999999</v>
+        <v>54.09</v>
       </c>
       <c r="D135" t="n">
-        <v>23244</v>
+        <v>25890</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>106.82</v>
+        <v>51.97</v>
       </c>
       <c r="B136" t="n">
-        <v>44993</v>
+        <v>22585</v>
       </c>
       <c r="C136" t="n">
-        <v>104.56</v>
+        <v>57.03</v>
       </c>
       <c r="D136" t="n">
-        <v>21361</v>
+        <v>28925</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>62</v>
+        <v>52.03</v>
       </c>
       <c r="B137" t="n">
-        <v>25070</v>
+        <v>19237</v>
       </c>
       <c r="C137" t="n">
-        <v>63.44</v>
+        <v>44.4</v>
       </c>
       <c r="D137" t="n">
-        <v>15916</v>
+        <v>19697</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>108.82</v>
+        <v>52.2</v>
       </c>
       <c r="B138" t="n">
-        <v>35795</v>
+        <v>20334</v>
       </c>
       <c r="C138" t="n">
-        <v>107</v>
+        <v>53.82</v>
       </c>
       <c r="D138" t="n">
-        <v>23647</v>
+        <v>24140</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>97.31</v>
+        <v>52.61</v>
       </c>
       <c r="B139" t="n">
-        <v>37376</v>
+        <v>21853</v>
       </c>
       <c r="C139" t="n">
-        <v>97.04000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="D139" t="n">
-        <v>12738</v>
+        <v>17067</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>99.37</v>
+        <v>52.67</v>
       </c>
       <c r="B140" t="n">
-        <v>43735</v>
+        <v>23110</v>
       </c>
       <c r="C140" t="n">
-        <v>97.94</v>
+        <v>44.62</v>
       </c>
       <c r="D140" t="n">
-        <v>24722</v>
+        <v>18422</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>105.67</v>
+        <v>52.77</v>
       </c>
       <c r="B141" t="n">
-        <v>44548</v>
+        <v>21526</v>
       </c>
       <c r="C141" t="n">
-        <v>109.02</v>
+        <v>60.11</v>
       </c>
       <c r="D141" t="n">
-        <v>17246</v>
+        <v>21052</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>104.67</v>
+        <v>52.84</v>
       </c>
       <c r="B142" t="n">
-        <v>43588</v>
+        <v>19143</v>
       </c>
       <c r="C142" t="n">
-        <v>101.77</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>28164</v>
+        <v>20704</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>102.45</v>
+        <v>52.85</v>
       </c>
       <c r="B143" t="n">
-        <v>49129</v>
+        <v>21113</v>
       </c>
       <c r="C143" t="n">
-        <v>107.18</v>
+        <v>55.66</v>
       </c>
       <c r="D143" t="n">
-        <v>29913</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>93.34999999999999</v>
+        <v>53.78</v>
       </c>
       <c r="B144" t="n">
-        <v>31475</v>
+        <v>20667</v>
       </c>
       <c r="C144" t="n">
-        <v>89.61</v>
+        <v>62.34</v>
       </c>
       <c r="D144" t="n">
-        <v>24349</v>
+        <v>10875</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>92.31999999999999</v>
+        <v>54.19</v>
       </c>
       <c r="B145" t="n">
-        <v>27321</v>
+        <v>21155</v>
       </c>
       <c r="C145" t="n">
-        <v>95.7</v>
+        <v>56.69</v>
       </c>
       <c r="D145" t="n">
-        <v>20834</v>
+        <v>17824</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>113.93</v>
+        <v>54.24</v>
       </c>
       <c r="B146" t="n">
-        <v>23912</v>
+        <v>21349</v>
       </c>
       <c r="C146" t="n">
-        <v>117.72</v>
+        <v>54.44</v>
       </c>
       <c r="D146" t="n">
-        <v>23810</v>
+        <v>21695</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>108.5</v>
+        <v>54.26</v>
       </c>
       <c r="B147" t="n">
-        <v>36443</v>
+        <v>20744</v>
       </c>
       <c r="C147" t="n">
-        <v>106.38</v>
+        <v>45.33</v>
       </c>
       <c r="D147" t="n">
-        <v>13608</v>
+        <v>10054</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>108.85</v>
+        <v>54.4</v>
       </c>
       <c r="B148" t="n">
-        <v>33723</v>
+        <v>21584</v>
       </c>
       <c r="C148" t="n">
-        <v>104.72</v>
+        <v>47.11</v>
       </c>
       <c r="D148" t="n">
-        <v>14714</v>
+        <v>16167</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>110.19</v>
+        <v>55.72</v>
       </c>
       <c r="B149" t="n">
-        <v>31362</v>
+        <v>21299</v>
       </c>
       <c r="C149" t="n">
-        <v>108.83</v>
+        <v>47.86</v>
       </c>
       <c r="D149" t="n">
-        <v>19971</v>
+        <v>18279</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>58.27</v>
+        <v>55.75</v>
       </c>
       <c r="B150" t="n">
-        <v>21907</v>
+        <v>20851</v>
       </c>
       <c r="C150" t="n">
-        <v>58.59</v>
+        <v>48.28</v>
       </c>
       <c r="D150" t="n">
-        <v>11728</v>
+        <v>10535</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>97.7</v>
+        <v>56.51</v>
       </c>
       <c r="B151" t="n">
-        <v>40585</v>
+        <v>18469</v>
       </c>
       <c r="C151" t="n">
-        <v>95.03</v>
+        <v>44.61</v>
       </c>
       <c r="D151" t="n">
-        <v>28723</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>37.7</v>
+        <v>57.6</v>
       </c>
       <c r="B152" t="n">
-        <v>25183</v>
+        <v>20746</v>
       </c>
       <c r="C152" t="n">
-        <v>38.73</v>
+        <v>48.65</v>
       </c>
       <c r="D152" t="n">
-        <v>15780</v>
+        <v>16069</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>106.5</v>
+        <v>59.48</v>
       </c>
       <c r="B153" t="n">
-        <v>42521</v>
+        <v>21855</v>
       </c>
       <c r="C153" t="n">
-        <v>104.95</v>
+        <v>49.13</v>
       </c>
       <c r="D153" t="n">
-        <v>12127</v>
+        <v>17509</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>102.68</v>
+        <v>59.55</v>
       </c>
       <c r="B154" t="n">
-        <v>44255</v>
+        <v>19248</v>
       </c>
       <c r="C154" t="n">
-        <v>99.26000000000001</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="D154" t="n">
-        <v>25712</v>
+        <v>21112</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>112.77</v>
+        <v>59.87</v>
       </c>
       <c r="B155" t="n">
-        <v>26523</v>
+        <v>20739</v>
       </c>
       <c r="C155" t="n">
-        <v>115.38</v>
+        <v>49.7</v>
       </c>
       <c r="D155" t="n">
-        <v>16399</v>
+        <v>19516</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>110.22</v>
+        <v>60.08</v>
       </c>
       <c r="B156" t="n">
-        <v>30139</v>
+        <v>22115</v>
       </c>
       <c r="C156" t="n">
-        <v>109.77</v>
+        <v>66.28</v>
       </c>
       <c r="D156" t="n">
-        <v>18775</v>
+        <v>24256</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>107.2</v>
+        <v>60.38</v>
       </c>
       <c r="B157" t="n">
-        <v>39622</v>
+        <v>19869</v>
       </c>
       <c r="C157" t="n">
-        <v>108.63</v>
+        <v>58.79</v>
       </c>
       <c r="D157" t="n">
-        <v>11358</v>
+        <v>17387</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>99.47</v>
+        <v>60.59</v>
       </c>
       <c r="B158" t="n">
-        <v>42690</v>
+        <v>20003</v>
       </c>
       <c r="C158" t="n">
-        <v>97.40000000000001</v>
+        <v>54.67</v>
       </c>
       <c r="D158" t="n">
-        <v>20455</v>
+        <v>20881</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>100.6</v>
+        <v>60.84</v>
       </c>
       <c r="B159" t="n">
-        <v>48165</v>
+        <v>22407</v>
       </c>
       <c r="C159" t="n">
-        <v>101.9</v>
+        <v>62.91</v>
       </c>
       <c r="D159" t="n">
-        <v>18144</v>
+        <v>28906</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>66.43000000000001</v>
+        <v>61.21</v>
       </c>
       <c r="B160" t="n">
-        <v>24459</v>
+        <v>20644</v>
       </c>
       <c r="C160" t="n">
-        <v>67.43000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="D160" t="n">
-        <v>11912</v>
+        <v>20171</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>91.79000000000001</v>
+        <v>61.67</v>
       </c>
       <c r="B161" t="n">
-        <v>26126</v>
+        <v>19736</v>
       </c>
       <c r="C161" t="n">
-        <v>91.55</v>
+        <v>69.53</v>
       </c>
       <c r="D161" t="n">
-        <v>26539</v>
+        <v>28576</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>87.83</v>
+        <v>61.7</v>
       </c>
       <c r="B162" t="n">
-        <v>21426</v>
+        <v>22111</v>
       </c>
       <c r="C162" t="n">
-        <v>87.31999999999999</v>
+        <v>35.76</v>
       </c>
       <c r="D162" t="n">
-        <v>18585</v>
+        <v>20386</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>113.61</v>
+        <v>62.15</v>
       </c>
       <c r="B163" t="n">
-        <v>22062</v>
+        <v>21134</v>
       </c>
       <c r="C163" t="n">
-        <v>115.04</v>
+        <v>63.94</v>
       </c>
       <c r="D163" t="n">
-        <v>29293</v>
+        <v>19387</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>108.39</v>
+        <v>62.3</v>
       </c>
       <c r="B164" t="n">
-        <v>36126</v>
+        <v>21447</v>
       </c>
       <c r="C164" t="n">
-        <v>106.33</v>
+        <v>63.56</v>
       </c>
       <c r="D164" t="n">
-        <v>24883</v>
+        <v>27287</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>99.52</v>
+        <v>62.45</v>
       </c>
       <c r="B165" t="n">
-        <v>44206</v>
+        <v>20775</v>
       </c>
       <c r="C165" t="n">
-        <v>101.08</v>
+        <v>58.04</v>
       </c>
       <c r="D165" t="n">
-        <v>17422</v>
+        <v>10481</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>112.96</v>
+        <v>62.97</v>
       </c>
       <c r="B166" t="n">
-        <v>24787</v>
+        <v>21101</v>
       </c>
       <c r="C166" t="n">
-        <v>111.84</v>
+        <v>57.86</v>
       </c>
       <c r="D166" t="n">
-        <v>11850</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>112.65</v>
+        <v>63.54</v>
       </c>
       <c r="B167" t="n">
-        <v>24529</v>
+        <v>20485</v>
       </c>
       <c r="C167" t="n">
-        <v>114.76</v>
+        <v>44.38</v>
       </c>
       <c r="D167" t="n">
-        <v>10326</v>
+        <v>10136</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>95.83</v>
+        <v>64.09</v>
       </c>
       <c r="B168" t="n">
-        <v>37920</v>
+        <v>20262</v>
       </c>
       <c r="C168" t="n">
-        <v>97.08</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="D168" t="n">
-        <v>24374</v>
+        <v>14855</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>104.53</v>
+        <v>64.17</v>
       </c>
       <c r="B169" t="n">
-        <v>50051</v>
+        <v>21044</v>
       </c>
       <c r="C169" t="n">
-        <v>105.8</v>
+        <v>54.41</v>
       </c>
       <c r="D169" t="n">
-        <v>10574</v>
+        <v>10860</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>105.82</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="B170" t="n">
-        <v>42908</v>
+        <v>20665</v>
       </c>
       <c r="C170" t="n">
-        <v>105.25</v>
+        <v>53.73</v>
       </c>
       <c r="D170" t="n">
-        <v>22161</v>
+        <v>28415</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>112.12</v>
+        <v>65.36</v>
       </c>
       <c r="B171" t="n">
-        <v>27939</v>
+        <v>20227</v>
       </c>
       <c r="C171" t="n">
-        <v>112.63</v>
+        <v>62.9</v>
       </c>
       <c r="D171" t="n">
-        <v>21660</v>
+        <v>23853</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>108.27</v>
+        <v>65.72</v>
       </c>
       <c r="B172" t="n">
-        <v>35933</v>
+        <v>20623</v>
       </c>
       <c r="C172" t="n">
-        <v>105.46</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="D172" t="n">
-        <v>25225</v>
+        <v>28841</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>101.43</v>
+        <v>66.34</v>
       </c>
       <c r="B173" t="n">
-        <v>44916</v>
+        <v>21373</v>
       </c>
       <c r="C173" t="n">
-        <v>100.6</v>
+        <v>79.73</v>
       </c>
       <c r="D173" t="n">
-        <v>14829</v>
+        <v>16975</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>71.59999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="B174" t="n">
-        <v>23040</v>
+        <v>19530</v>
       </c>
       <c r="C174" t="n">
-        <v>73.2</v>
+        <v>57.56</v>
       </c>
       <c r="D174" t="n">
-        <v>26064</v>
+        <v>15393</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>99.87</v>
+        <v>67.62</v>
       </c>
       <c r="B175" t="n">
-        <v>44193</v>
+        <v>19474</v>
       </c>
       <c r="C175" t="n">
-        <v>103.09</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="D175" t="n">
-        <v>11690</v>
+        <v>27850</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>93.56999999999999</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="B176" t="n">
-        <v>28290</v>
+        <v>19640</v>
       </c>
       <c r="C176" t="n">
-        <v>91.51000000000001</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="D176" t="n">
-        <v>24145</v>
+        <v>17134</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>92.11</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="B177" t="n">
-        <v>25189</v>
+        <v>19933</v>
       </c>
       <c r="C177" t="n">
-        <v>93.61</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="D177" t="n">
-        <v>29453</v>
+        <v>25720</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>157.58</v>
+        <v>69.34</v>
       </c>
       <c r="B178" t="n">
-        <v>23272</v>
+        <v>22065</v>
       </c>
       <c r="C178" t="n">
-        <v>153.02</v>
+        <v>72.55</v>
       </c>
       <c r="D178" t="n">
-        <v>19823</v>
+        <v>14319</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>173.39</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="B179" t="n">
-        <v>21921</v>
+        <v>21953</v>
       </c>
       <c r="C179" t="n">
-        <v>174.1</v>
+        <v>85.67</v>
       </c>
       <c r="D179" t="n">
-        <v>11112</v>
+        <v>28168</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>112.28</v>
+        <v>69.63</v>
       </c>
       <c r="B180" t="n">
-        <v>28242</v>
+        <v>21428</v>
       </c>
       <c r="C180" t="n">
-        <v>114.92</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="D180" t="n">
-        <v>17432</v>
+        <v>28235</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>100.04</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="B181" t="n">
-        <v>46190</v>
+        <v>20678</v>
       </c>
       <c r="C181" t="n">
-        <v>98.92</v>
+        <v>59.53</v>
       </c>
       <c r="D181" t="n">
-        <v>11364</v>
+        <v>21351</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>91.25</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="B182" t="n">
-        <v>24631</v>
+        <v>21431</v>
       </c>
       <c r="C182" t="n">
-        <v>91.77</v>
+        <v>75.23</v>
       </c>
       <c r="D182" t="n">
-        <v>16219</v>
+        <v>24150</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>97.79000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="B183" t="n">
-        <v>42155</v>
+        <v>20485</v>
       </c>
       <c r="C183" t="n">
-        <v>98.41</v>
+        <v>59.02</v>
       </c>
       <c r="D183" t="n">
-        <v>23992</v>
+        <v>23694</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>96.09</v>
+        <v>70.55</v>
       </c>
       <c r="B184" t="n">
-        <v>38539</v>
+        <v>20241</v>
       </c>
       <c r="C184" t="n">
-        <v>99.34999999999999</v>
+        <v>73.61</v>
       </c>
       <c r="D184" t="n">
-        <v>11214</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>35.24</v>
+        <v>70.59</v>
       </c>
       <c r="B185" t="n">
-        <v>23405</v>
+        <v>19814</v>
       </c>
       <c r="C185" t="n">
-        <v>34.71</v>
+        <v>55.94</v>
       </c>
       <c r="D185" t="n">
-        <v>11436</v>
+        <v>28658</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>92.61</v>
+        <v>70.94</v>
       </c>
       <c r="B186" t="n">
-        <v>29851</v>
+        <v>19729</v>
       </c>
       <c r="C186" t="n">
-        <v>92.3</v>
+        <v>84.08</v>
       </c>
       <c r="D186" t="n">
-        <v>21920</v>
+        <v>28343</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>109.8</v>
+        <v>71.25</v>
       </c>
       <c r="B187" t="n">
-        <v>31896</v>
+        <v>21921</v>
       </c>
       <c r="C187" t="n">
-        <v>109.2</v>
+        <v>73.27</v>
       </c>
       <c r="D187" t="n">
-        <v>26864</v>
+        <v>18755</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>94.59</v>
+        <v>71.52</v>
       </c>
       <c r="B188" t="n">
-        <v>30878</v>
+        <v>19429</v>
       </c>
       <c r="C188" t="n">
-        <v>93.62</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D188" t="n">
-        <v>22861</v>
+        <v>24055</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>94.28</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="B189" t="n">
-        <v>31652</v>
+        <v>20855</v>
       </c>
       <c r="C189" t="n">
-        <v>91.93000000000001</v>
+        <v>82.75</v>
       </c>
       <c r="D189" t="n">
-        <v>24036</v>
+        <v>22059</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>99.14</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="B190" t="n">
-        <v>43304</v>
+        <v>21461</v>
       </c>
       <c r="C190" t="n">
-        <v>98.84</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D190" t="n">
-        <v>17375</v>
+        <v>20950</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>111.81</v>
+        <v>71.77</v>
       </c>
       <c r="B191" t="n">
-        <v>27696</v>
+        <v>19539</v>
       </c>
       <c r="C191" t="n">
-        <v>112.82</v>
+        <v>83.42</v>
       </c>
       <c r="D191" t="n">
-        <v>29697</v>
+        <v>16281</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>178.71</v>
+        <v>72.05</v>
       </c>
       <c r="B192" t="n">
-        <v>21793</v>
+        <v>20298</v>
       </c>
       <c r="C192" t="n">
-        <v>180</v>
+        <v>98.59</v>
       </c>
       <c r="D192" t="n">
-        <v>15430</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>52.68</v>
+        <v>72.39</v>
       </c>
       <c r="B193" t="n">
-        <v>25378</v>
+        <v>22271</v>
       </c>
       <c r="C193" t="n">
-        <v>50.93</v>
+        <v>78.67</v>
       </c>
       <c r="D193" t="n">
-        <v>17386</v>
+        <v>29635</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>99.68000000000001</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="B194" t="n">
-        <v>43325</v>
+        <v>20651</v>
       </c>
       <c r="C194" t="n">
-        <v>96.31999999999999</v>
+        <v>58.88</v>
       </c>
       <c r="D194" t="n">
-        <v>18314</v>
+        <v>19508</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>107.96</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="B195" t="n">
-        <v>38245</v>
+        <v>19829</v>
       </c>
       <c r="C195" t="n">
-        <v>111.36</v>
+        <v>72.62</v>
       </c>
       <c r="D195" t="n">
-        <v>29572</v>
+        <v>13451</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>98.98</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="B196" t="n">
-        <v>41022</v>
+        <v>20403</v>
       </c>
       <c r="C196" t="n">
-        <v>98.2</v>
+        <v>81.02</v>
       </c>
       <c r="D196" t="n">
-        <v>23412</v>
+        <v>28984</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>93.11</v>
+        <v>73.28</v>
       </c>
       <c r="B197" t="n">
-        <v>28088</v>
+        <v>19952</v>
       </c>
       <c r="C197" t="n">
-        <v>93.08</v>
+        <v>65.38</v>
       </c>
       <c r="D197" t="n">
-        <v>10646</v>
+        <v>13164</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>102.18</v>
+        <v>73.58</v>
       </c>
       <c r="B198" t="n">
-        <v>45075</v>
+        <v>20564</v>
       </c>
       <c r="C198" t="n">
-        <v>101.66</v>
+        <v>78.89</v>
       </c>
       <c r="D198" t="n">
-        <v>25660</v>
+        <v>10204</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>111.28</v>
+        <v>73.67</v>
       </c>
       <c r="B199" t="n">
-        <v>27481</v>
+        <v>21035</v>
       </c>
       <c r="C199" t="n">
-        <v>112.96</v>
+        <v>62.12</v>
       </c>
       <c r="D199" t="n">
-        <v>11883</v>
+        <v>23938</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>107.96</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="B200" t="n">
-        <v>40045</v>
+        <v>19860</v>
       </c>
       <c r="C200" t="n">
-        <v>106.58</v>
+        <v>65.53</v>
       </c>
       <c r="D200" t="n">
-        <v>27887</v>
+        <v>18403</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>28.45</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="B201" t="n">
-        <v>23481</v>
+        <v>20079</v>
       </c>
       <c r="C201" t="n">
-        <v>28.17</v>
+        <v>62.5</v>
       </c>
       <c r="D201" t="n">
-        <v>12070</v>
+        <v>19536</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>112.76</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="B202" t="n">
-        <v>26071</v>
+        <v>20995</v>
       </c>
       <c r="C202" t="n">
-        <v>112.37</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="D202" t="n">
-        <v>10041</v>
+        <v>22507</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>89.76000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="B203" t="n">
-        <v>24230</v>
+        <v>21108</v>
       </c>
       <c r="C203" t="n">
-        <v>90.98</v>
+        <v>83.45</v>
       </c>
       <c r="D203" t="n">
-        <v>26171</v>
+        <v>26157</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>94.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="B204" t="n">
-        <v>31320</v>
+        <v>19891</v>
       </c>
       <c r="C204" t="n">
-        <v>95.61</v>
+        <v>68.11</v>
       </c>
       <c r="D204" t="n">
-        <v>20797</v>
+        <v>21887</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113.8</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="B205" t="n">
-        <v>25334</v>
+        <v>20517</v>
       </c>
       <c r="C205" t="n">
-        <v>117.03</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="D205" t="n">
-        <v>11330</v>
+        <v>13499</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>106.56</v>
+        <v>77.8</v>
       </c>
       <c r="B206" t="n">
-        <v>41649</v>
+        <v>20736</v>
       </c>
       <c r="C206" t="n">
-        <v>104.8</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="D206" t="n">
-        <v>26943</v>
+        <v>15702</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>99.08</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="B207" t="n">
-        <v>45315</v>
+        <v>20335</v>
       </c>
       <c r="C207" t="n">
-        <v>100.17</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="D207" t="n">
-        <v>19579</v>
+        <v>22929</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>92.44</v>
+        <v>79.66</v>
       </c>
       <c r="B208" t="n">
-        <v>28097</v>
+        <v>19534</v>
       </c>
       <c r="C208" t="n">
-        <v>95.48</v>
+        <v>68.22</v>
       </c>
       <c r="D208" t="n">
-        <v>11461</v>
+        <v>29591</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>90.02</v>
+        <v>80.06</v>
       </c>
       <c r="B209" t="n">
-        <v>25782</v>
+        <v>20676</v>
       </c>
       <c r="C209" t="n">
-        <v>87.61</v>
+        <v>71.06</v>
       </c>
       <c r="D209" t="n">
-        <v>24912</v>
+        <v>18283</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>32.22</v>
+        <v>80.22</v>
       </c>
       <c r="B210" t="n">
-        <v>26557</v>
+        <v>20448</v>
       </c>
       <c r="C210" t="n">
-        <v>31.66</v>
+        <v>66.17</v>
       </c>
       <c r="D210" t="n">
-        <v>16676</v>
+        <v>11390</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>114.03</v>
+        <v>80.23</v>
       </c>
       <c r="B211" t="n">
-        <v>24801</v>
+        <v>20623</v>
       </c>
       <c r="C211" t="n">
-        <v>112.34</v>
+        <v>75.86</v>
       </c>
       <c r="D211" t="n">
-        <v>29841</v>
+        <v>20268</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>100.07</v>
+        <v>80.41</v>
       </c>
       <c r="B212" t="n">
-        <v>45003</v>
+        <v>20165</v>
       </c>
       <c r="C212" t="n">
-        <v>99.84</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="D212" t="n">
-        <v>25771</v>
+        <v>24039</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>106.19</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="B213" t="n">
-        <v>44529</v>
+        <v>20793</v>
       </c>
       <c r="C213" t="n">
-        <v>106.98</v>
+        <v>61.48</v>
       </c>
       <c r="D213" t="n">
-        <v>20166</v>
+        <v>25010</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>103.36</v>
+        <v>80.72</v>
       </c>
       <c r="B214" t="n">
-        <v>46787</v>
+        <v>20304</v>
       </c>
       <c r="C214" t="n">
-        <v>105.98</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="D214" t="n">
-        <v>24122</v>
+        <v>10131</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>99.36</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="B215" t="n">
-        <v>44488</v>
+        <v>20241</v>
       </c>
       <c r="C215" t="n">
-        <v>98</v>
+        <v>82.44</v>
       </c>
       <c r="D215" t="n">
-        <v>13362</v>
+        <v>15639</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>98.84</v>
+        <v>81.08</v>
       </c>
       <c r="B216" t="n">
-        <v>42963</v>
+        <v>20052</v>
       </c>
       <c r="C216" t="n">
-        <v>102.25</v>
+        <v>90.45</v>
       </c>
       <c r="D216" t="n">
-        <v>21837</v>
+        <v>17385</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>93.62</v>
+        <v>81.16</v>
       </c>
       <c r="B217" t="n">
-        <v>28064</v>
+        <v>20378</v>
       </c>
       <c r="C217" t="n">
-        <v>91.25</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D217" t="n">
-        <v>17997</v>
+        <v>10842</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>96.78</v>
+        <v>81.5</v>
       </c>
       <c r="B218" t="n">
-        <v>41570</v>
+        <v>20322</v>
       </c>
       <c r="C218" t="n">
-        <v>93.25</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D218" t="n">
-        <v>13655</v>
+        <v>24697</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>98.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="B219" t="n">
-        <v>42399</v>
+        <v>19101</v>
       </c>
       <c r="C219" t="n">
-        <v>95.52</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D219" t="n">
-        <v>19039</v>
+        <v>22031</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>102.35</v>
+        <v>82.63</v>
       </c>
       <c r="B220" t="n">
-        <v>45567</v>
+        <v>20087</v>
       </c>
       <c r="C220" t="n">
-        <v>99.59</v>
+        <v>89.2</v>
       </c>
       <c r="D220" t="n">
-        <v>29231</v>
+        <v>14973</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>98.78</v>
+        <v>82.64</v>
       </c>
       <c r="B221" t="n">
-        <v>41941</v>
+        <v>20003</v>
       </c>
       <c r="C221" t="n">
-        <v>96.15000000000001</v>
+        <v>85.17</v>
       </c>
       <c r="D221" t="n">
-        <v>10171</v>
+        <v>28683</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>100.56</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="B222" t="n">
-        <v>45125</v>
+        <v>20649</v>
       </c>
       <c r="C222" t="n">
-        <v>98.81</v>
+        <v>70.16</v>
       </c>
       <c r="D222" t="n">
-        <v>25985</v>
+        <v>26605</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>161.94</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="B223" t="n">
-        <v>26482</v>
+        <v>19548</v>
       </c>
       <c r="C223" t="n">
-        <v>162.83</v>
+        <v>81</v>
       </c>
       <c r="D223" t="n">
-        <v>14464</v>
+        <v>22834</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>111.71</v>
+        <v>83.44</v>
       </c>
       <c r="B224" t="n">
-        <v>27479</v>
+        <v>19404</v>
       </c>
       <c r="C224" t="n">
-        <v>112.44</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="D224" t="n">
-        <v>28056</v>
+        <v>12017</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>111.98</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="B225" t="n">
-        <v>28105</v>
+        <v>20337</v>
       </c>
       <c r="C225" t="n">
-        <v>113.39</v>
+        <v>102.25</v>
       </c>
       <c r="D225" t="n">
-        <v>14148</v>
+        <v>21742</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0.95</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="B226" t="n">
-        <v>25780</v>
+        <v>19313</v>
       </c>
       <c r="C226" t="n">
-        <v>0.59</v>
+        <v>106.02</v>
       </c>
       <c r="D226" t="n">
-        <v>20809</v>
+        <v>29099</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>104.17</v>
+        <v>84.03</v>
       </c>
       <c r="B227" t="n">
-        <v>46782</v>
+        <v>20487</v>
       </c>
       <c r="C227" t="n">
-        <v>104.29</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="D227" t="n">
-        <v>22292</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>96.95999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="B228" t="n">
-        <v>38988</v>
+        <v>19997</v>
       </c>
       <c r="C228" t="n">
-        <v>95.28</v>
+        <v>94.62</v>
       </c>
       <c r="D228" t="n">
-        <v>21081</v>
+        <v>28613</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>96.63</v>
+        <v>86.02</v>
       </c>
       <c r="B229" t="n">
-        <v>37379</v>
+        <v>20314</v>
       </c>
       <c r="C229" t="n">
-        <v>98.17</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="D229" t="n">
-        <v>20572</v>
+        <v>16095</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>103.29</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="B230" t="n">
-        <v>47990</v>
+        <v>20298</v>
       </c>
       <c r="C230" t="n">
-        <v>99.81</v>
+        <v>90.8</v>
       </c>
       <c r="D230" t="n">
-        <v>19690</v>
+        <v>29680</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>112.33</v>
+        <v>86.55</v>
       </c>
       <c r="B231" t="n">
-        <v>27117</v>
+        <v>20459</v>
       </c>
       <c r="C231" t="n">
-        <v>113.1</v>
+        <v>90.41</v>
       </c>
       <c r="D231" t="n">
-        <v>24572</v>
+        <v>17231</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>105.1</v>
+        <v>86.88</v>
       </c>
       <c r="B232" t="n">
-        <v>46044</v>
+        <v>20052</v>
       </c>
       <c r="C232" t="n">
-        <v>105.61</v>
+        <v>110.05</v>
       </c>
       <c r="D232" t="n">
-        <v>28120</v>
+        <v>14162</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>111.63</v>
+        <v>87.36</v>
       </c>
       <c r="B233" t="n">
-        <v>26654</v>
+        <v>21112</v>
       </c>
       <c r="C233" t="n">
-        <v>112.09</v>
+        <v>110.06</v>
       </c>
       <c r="D233" t="n">
-        <v>10213</v>
+        <v>25338</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>66.20999999999999</v>
+        <v>88.59</v>
       </c>
       <c r="B234" t="n">
-        <v>19611</v>
+        <v>20428</v>
       </c>
       <c r="C234" t="n">
-        <v>67.77</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D234" t="n">
-        <v>20136</v>
+        <v>20665</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>107.74</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="B235" t="n">
-        <v>39340</v>
+        <v>20680</v>
       </c>
       <c r="C235" t="n">
-        <v>106.64</v>
+        <v>94.42</v>
       </c>
       <c r="D235" t="n">
-        <v>26680</v>
+        <v>22255</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>92.09</v>
+        <v>89.38</v>
       </c>
       <c r="B236" t="n">
-        <v>25852</v>
+        <v>20526</v>
       </c>
       <c r="C236" t="n">
-        <v>94.61</v>
+        <v>105.65</v>
       </c>
       <c r="D236" t="n">
-        <v>23278</v>
+        <v>28047</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>98.29000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="B237" t="n">
-        <v>42795</v>
+        <v>20531</v>
       </c>
       <c r="C237" t="n">
-        <v>96.29000000000001</v>
+        <v>94.14</v>
       </c>
       <c r="D237" t="n">
-        <v>29501</v>
+        <v>29120</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>103.51</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="B238" t="n">
-        <v>45315</v>
+        <v>20899</v>
       </c>
       <c r="C238" t="n">
-        <v>104.29</v>
+        <v>110.95</v>
       </c>
       <c r="D238" t="n">
-        <v>16846</v>
+        <v>26949</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>108.07</v>
+        <v>90.16</v>
       </c>
       <c r="B239" t="n">
-        <v>39621</v>
+        <v>20376</v>
       </c>
       <c r="C239" t="n">
-        <v>106.52</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="D239" t="n">
-        <v>20590</v>
+        <v>16438</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>162.8</v>
+        <v>90.3</v>
       </c>
       <c r="B240" t="n">
-        <v>23331</v>
+        <v>19811</v>
       </c>
       <c r="C240" t="n">
-        <v>163.2</v>
+        <v>84.73</v>
       </c>
       <c r="D240" t="n">
-        <v>16233</v>
+        <v>16395</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>97.03</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="B241" t="n">
-        <v>39199</v>
+        <v>20676</v>
       </c>
       <c r="C241" t="n">
-        <v>96.06</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="D241" t="n">
-        <v>26039</v>
+        <v>24424</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>90.23</v>
+        <v>90.75</v>
       </c>
       <c r="B242" t="n">
-        <v>23328</v>
+        <v>20231</v>
       </c>
       <c r="C242" t="n">
-        <v>85.70999999999999</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="D242" t="n">
-        <v>20996</v>
+        <v>12385</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>107.41</v>
+        <v>91.03</v>
       </c>
       <c r="B243" t="n">
-        <v>40271</v>
+        <v>20427</v>
       </c>
       <c r="C243" t="n">
-        <v>104.03</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D243" t="n">
-        <v>28566</v>
+        <v>14093</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>110.32</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="B244" t="n">
-        <v>32574</v>
+        <v>21408</v>
       </c>
       <c r="C244" t="n">
-        <v>110.35</v>
+        <v>83.67</v>
       </c>
       <c r="D244" t="n">
-        <v>14049</v>
+        <v>24956</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>106.94</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="B245" t="n">
-        <v>38857</v>
+        <v>21337</v>
       </c>
       <c r="C245" t="n">
-        <v>102.79</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="D245" t="n">
-        <v>24498</v>
+        <v>18653</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>110.01</v>
+        <v>91.72</v>
       </c>
       <c r="B246" t="n">
-        <v>32468</v>
+        <v>21652</v>
       </c>
       <c r="C246" t="n">
-        <v>109.57</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D246" t="n">
-        <v>17487</v>
+        <v>10390</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>91.48999999999999</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="B247" t="n">
-        <v>27596</v>
+        <v>20927</v>
       </c>
       <c r="C247" t="n">
-        <v>93.47</v>
+        <v>87</v>
       </c>
       <c r="D247" t="n">
-        <v>27613</v>
+        <v>20144</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>95.38</v>
+        <v>92.05</v>
       </c>
       <c r="B248" t="n">
-        <v>33803</v>
+        <v>21832</v>
       </c>
       <c r="C248" t="n">
-        <v>96.87</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>24094</v>
+        <v>17542</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>46.94</v>
+        <v>93.12</v>
       </c>
       <c r="B249" t="n">
-        <v>23194</v>
+        <v>22687</v>
       </c>
       <c r="C249" t="n">
-        <v>44.87</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D249" t="n">
-        <v>19675</v>
+        <v>27968</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>100.22</v>
+        <v>93.27</v>
       </c>
       <c r="B250" t="n">
-        <v>42184</v>
+        <v>22962</v>
       </c>
       <c r="C250" t="n">
-        <v>98.02</v>
+        <v>91.28</v>
       </c>
       <c r="D250" t="n">
-        <v>22643</v>
+        <v>20785</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>146.78</v>
+        <v>93.45</v>
       </c>
       <c r="B251" t="n">
-        <v>21718</v>
+        <v>22573</v>
       </c>
       <c r="C251" t="n">
-        <v>146.64</v>
+        <v>98.66</v>
       </c>
       <c r="D251" t="n">
-        <v>28493</v>
+        <v>11039</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>173.91</v>
+        <v>94</v>
       </c>
       <c r="B252" t="n">
-        <v>24099</v>
+        <v>23748</v>
       </c>
       <c r="C252" t="n">
-        <v>167.58</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D252" t="n">
-        <v>27060</v>
+        <v>22134</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>121.14</v>
+        <v>94.38</v>
       </c>
       <c r="B253" t="n">
-        <v>24537</v>
+        <v>23550</v>
       </c>
       <c r="C253" t="n">
-        <v>119.42</v>
+        <v>82.89</v>
       </c>
       <c r="D253" t="n">
-        <v>19228</v>
+        <v>18076</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96.3</v>
+        <v>94.69</v>
       </c>
       <c r="B254" t="n">
-        <v>36383</v>
+        <v>24660</v>
       </c>
       <c r="C254" t="n">
-        <v>93.37</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="D254" t="n">
-        <v>14138</v>
+        <v>11198</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>108.45</v>
+        <v>94.86</v>
       </c>
       <c r="B255" t="n">
-        <v>36340</v>
+        <v>25150</v>
       </c>
       <c r="C255" t="n">
-        <v>110.68</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="D255" t="n">
-        <v>24759</v>
+        <v>26647</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>114.76</v>
+        <v>94.91</v>
       </c>
       <c r="B256" t="n">
-        <v>22872</v>
+        <v>25126</v>
       </c>
       <c r="C256" t="n">
-        <v>117.57</v>
+        <v>83.33</v>
       </c>
       <c r="D256" t="n">
-        <v>22790</v>
+        <v>17952</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>111.44</v>
+        <v>95.17</v>
       </c>
       <c r="B257" t="n">
-        <v>28625</v>
+        <v>25930</v>
       </c>
       <c r="C257" t="n">
-        <v>114.14</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="D257" t="n">
-        <v>13846</v>
+        <v>28432</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>103.35</v>
+        <v>95.45</v>
       </c>
       <c r="B258" t="n">
-        <v>46785</v>
+        <v>25406</v>
       </c>
       <c r="C258" t="n">
-        <v>107.93</v>
+        <v>86.8</v>
       </c>
       <c r="D258" t="n">
-        <v>23260</v>
+        <v>23087</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>90.66</v>
+        <v>95.58</v>
       </c>
       <c r="B259" t="n">
-        <v>22955</v>
+        <v>26396</v>
       </c>
       <c r="C259" t="n">
-        <v>90.73999999999999</v>
+        <v>110.55</v>
       </c>
       <c r="D259" t="n">
-        <v>12101</v>
+        <v>23337</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>108.52</v>
+        <v>95.81</v>
       </c>
       <c r="B260" t="n">
-        <v>35195</v>
+        <v>25927</v>
       </c>
       <c r="C260" t="n">
-        <v>105.12</v>
+        <v>91.09</v>
       </c>
       <c r="D260" t="n">
-        <v>16991</v>
+        <v>15162</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>94.02</v>
+        <v>96.45</v>
       </c>
       <c r="B261" t="n">
-        <v>28810</v>
+        <v>27173</v>
       </c>
       <c r="C261" t="n">
-        <v>95.54000000000001</v>
+        <v>97.97</v>
       </c>
       <c r="D261" t="n">
-        <v>24855</v>
+        <v>26332</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>95.28</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="B262" t="n">
-        <v>36945</v>
+        <v>28025</v>
       </c>
       <c r="C262" t="n">
-        <v>99.88</v>
+        <v>114.52</v>
       </c>
       <c r="D262" t="n">
-        <v>26930</v>
+        <v>16271</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>99.76000000000001</v>
+        <v>96.58</v>
       </c>
       <c r="B263" t="n">
-        <v>43793</v>
+        <v>28473</v>
       </c>
       <c r="C263" t="n">
-        <v>98.7</v>
+        <v>86.25</v>
       </c>
       <c r="D263" t="n">
-        <v>27128</v>
+        <v>15345</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>134.19</v>
+        <v>96.63</v>
       </c>
       <c r="B264" t="n">
-        <v>20029</v>
+        <v>28599</v>
       </c>
       <c r="C264" t="n">
-        <v>131.67</v>
+        <v>91.75</v>
       </c>
       <c r="D264" t="n">
-        <v>13514</v>
+        <v>25499</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>90.5</v>
+        <v>97.38</v>
       </c>
       <c r="B265" t="n">
-        <v>23236</v>
+        <v>29625</v>
       </c>
       <c r="C265" t="n">
-        <v>90.36</v>
+        <v>99.53</v>
       </c>
       <c r="D265" t="n">
-        <v>28577</v>
+        <v>19420</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>110.4</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="B266" t="n">
-        <v>28829</v>
+        <v>29993</v>
       </c>
       <c r="C266" t="n">
-        <v>112.98</v>
+        <v>112.6</v>
       </c>
       <c r="D266" t="n">
-        <v>10671</v>
+        <v>17443</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>169.63</v>
+        <v>97.75</v>
       </c>
       <c r="B267" t="n">
-        <v>21777</v>
+        <v>31723</v>
       </c>
       <c r="C267" t="n">
-        <v>167.47</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="D267" t="n">
-        <v>13788</v>
+        <v>24601</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>96.54000000000001</v>
+        <v>98.27</v>
       </c>
       <c r="B268" t="n">
-        <v>38544</v>
+        <v>31858</v>
       </c>
       <c r="C268" t="n">
-        <v>96</v>
+        <v>100.61</v>
       </c>
       <c r="D268" t="n">
-        <v>19565</v>
+        <v>20561</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>175.18</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="B269" t="n">
-        <v>22541</v>
+        <v>31497</v>
       </c>
       <c r="C269" t="n">
-        <v>177.17</v>
+        <v>112.74</v>
       </c>
       <c r="D269" t="n">
-        <v>19248</v>
+        <v>12488</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>104.52</v>
+        <v>98.58</v>
       </c>
       <c r="B270" t="n">
-        <v>47272</v>
+        <v>32618</v>
       </c>
       <c r="C270" t="n">
-        <v>104.97</v>
+        <v>80.22</v>
       </c>
       <c r="D270" t="n">
-        <v>11129</v>
+        <v>27449</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>90.62</v>
+        <v>98.94</v>
       </c>
       <c r="B271" t="n">
-        <v>22817</v>
+        <v>32586</v>
       </c>
       <c r="C271" t="n">
-        <v>89.11</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="D271" t="n">
-        <v>18420</v>
+        <v>25625</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>109.7</v>
+        <v>99.95</v>
       </c>
       <c r="B272" t="n">
-        <v>34482</v>
+        <v>34038</v>
       </c>
       <c r="C272" t="n">
-        <v>106.77</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="D272" t="n">
-        <v>14409</v>
+        <v>29280</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>40.08</v>
+        <v>100.52</v>
       </c>
       <c r="B273" t="n">
-        <v>23401</v>
+        <v>35929</v>
       </c>
       <c r="C273" t="n">
-        <v>40.11</v>
+        <v>90.31</v>
       </c>
       <c r="D273" t="n">
-        <v>16927</v>
+        <v>16706</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>113.2</v>
+        <v>100.88</v>
       </c>
       <c r="B274" t="n">
-        <v>26464</v>
+        <v>36902</v>
       </c>
       <c r="C274" t="n">
-        <v>111.46</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="D274" t="n">
-        <v>19454</v>
+        <v>14878</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>90.28</v>
+        <v>100.96</v>
       </c>
       <c r="B275" t="n">
-        <v>21282</v>
+        <v>37169</v>
       </c>
       <c r="C275" t="n">
-        <v>90.11</v>
+        <v>103.94</v>
       </c>
       <c r="D275" t="n">
-        <v>28741</v>
+        <v>21262</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>97.77</v>
+        <v>101.03</v>
       </c>
       <c r="B276" t="n">
-        <v>41349</v>
+        <v>36271</v>
       </c>
       <c r="C276" t="n">
-        <v>99.98</v>
+        <v>99.3</v>
       </c>
       <c r="D276" t="n">
-        <v>25095</v>
+        <v>26399</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>102.49</v>
+        <v>101.57</v>
       </c>
       <c r="B277" t="n">
-        <v>46380</v>
+        <v>37265</v>
       </c>
       <c r="C277" t="n">
-        <v>102.82</v>
+        <v>92.11</v>
       </c>
       <c r="D277" t="n">
-        <v>27856</v>
+        <v>23290</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>25.58</v>
+        <v>101.7</v>
       </c>
       <c r="B278" t="n">
-        <v>21374</v>
+        <v>37021</v>
       </c>
       <c r="C278" t="n">
-        <v>26.15</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="D278" t="n">
-        <v>27855</v>
+        <v>21623</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>94.16</v>
+        <v>101.72</v>
       </c>
       <c r="B279" t="n">
-        <v>33595</v>
+        <v>36886</v>
       </c>
       <c r="C279" t="n">
-        <v>91.86</v>
+        <v>102.02</v>
       </c>
       <c r="D279" t="n">
-        <v>27799</v>
+        <v>14926</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>170.19</v>
+        <v>101.73</v>
       </c>
       <c r="B280" t="n">
-        <v>21506</v>
+        <v>36469</v>
       </c>
       <c r="C280" t="n">
-        <v>170.52</v>
+        <v>112.76</v>
       </c>
       <c r="D280" t="n">
-        <v>26193</v>
+        <v>16849</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>59.45</v>
+        <v>102.28</v>
       </c>
       <c r="B281" t="n">
-        <v>23690</v>
+        <v>37878</v>
       </c>
       <c r="C281" t="n">
-        <v>57.83</v>
+        <v>109.91</v>
       </c>
       <c r="D281" t="n">
-        <v>10607</v>
+        <v>27892</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>94.23</v>
+        <v>102.45</v>
       </c>
       <c r="B282" t="n">
-        <v>32624</v>
+        <v>36920</v>
       </c>
       <c r="C282" t="n">
-        <v>94.78</v>
+        <v>104.38</v>
       </c>
       <c r="D282" t="n">
-        <v>18184</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>109.02</v>
+        <v>102.97</v>
       </c>
       <c r="B283" t="n">
-        <v>36497</v>
+        <v>37990</v>
       </c>
       <c r="C283" t="n">
-        <v>109.3</v>
+        <v>106.17</v>
       </c>
       <c r="D283" t="n">
-        <v>27143</v>
+        <v>18604</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>104.78</v>
+        <v>103.33</v>
       </c>
       <c r="B284" t="n">
-        <v>43789</v>
+        <v>38041</v>
       </c>
       <c r="C284" t="n">
-        <v>108.53</v>
+        <v>96.09</v>
       </c>
       <c r="D284" t="n">
-        <v>25884</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>103.7</v>
+        <v>103.74</v>
       </c>
       <c r="B285" t="n">
-        <v>50145</v>
+        <v>37175</v>
       </c>
       <c r="C285" t="n">
-        <v>100.01</v>
+        <v>101.91</v>
       </c>
       <c r="D285" t="n">
-        <v>20916</v>
+        <v>23757</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>94.51000000000001</v>
+        <v>104.39</v>
       </c>
       <c r="B286" t="n">
-        <v>32513</v>
+        <v>38109</v>
       </c>
       <c r="C286" t="n">
-        <v>95.19</v>
+        <v>101.7</v>
       </c>
       <c r="D286" t="n">
-        <v>18858</v>
+        <v>26894</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>100.65</v>
+        <v>105.55</v>
       </c>
       <c r="B287" t="n">
-        <v>45381</v>
+        <v>36925</v>
       </c>
       <c r="C287" t="n">
-        <v>102.75</v>
+        <v>107.32</v>
       </c>
       <c r="D287" t="n">
-        <v>22274</v>
+        <v>27195</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>112.47</v>
+        <v>105.98</v>
       </c>
       <c r="B288" t="n">
-        <v>25025</v>
+        <v>34177</v>
       </c>
       <c r="C288" t="n">
-        <v>110.01</v>
+        <v>108.17</v>
       </c>
       <c r="D288" t="n">
-        <v>26671</v>
+        <v>10506</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>103.43</v>
+        <v>106.04</v>
       </c>
       <c r="B289" t="n">
-        <v>48618</v>
+        <v>34711</v>
       </c>
       <c r="C289" t="n">
-        <v>107</v>
+        <v>123.63</v>
       </c>
       <c r="D289" t="n">
-        <v>29036</v>
+        <v>11941</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>114.9</v>
+        <v>106.05</v>
       </c>
       <c r="B290" t="n">
-        <v>21753</v>
+        <v>34704</v>
       </c>
       <c r="C290" t="n">
-        <v>115.43</v>
+        <v>105.23</v>
       </c>
       <c r="D290" t="n">
-        <v>11470</v>
+        <v>12885</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>114.88</v>
+        <v>106.44</v>
       </c>
       <c r="B291" t="n">
-        <v>23463</v>
+        <v>33928</v>
       </c>
       <c r="C291" t="n">
-        <v>114.79</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D291" t="n">
-        <v>25979</v>
+        <v>24912</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>103.11</v>
+        <v>107.02</v>
       </c>
       <c r="B292" t="n">
-        <v>47758</v>
+        <v>33246</v>
       </c>
       <c r="C292" t="n">
-        <v>103.25</v>
+        <v>109.25</v>
       </c>
       <c r="D292" t="n">
-        <v>11736</v>
+        <v>10726</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>99.22</v>
+        <v>107.49</v>
       </c>
       <c r="B293" t="n">
-        <v>42850</v>
+        <v>32282</v>
       </c>
       <c r="C293" t="n">
-        <v>102.79</v>
+        <v>128.32</v>
       </c>
       <c r="D293" t="n">
-        <v>19498</v>
+        <v>29720</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>96.15000000000001</v>
+        <v>107.55</v>
       </c>
       <c r="B294" t="n">
-        <v>34542</v>
+        <v>31322</v>
       </c>
       <c r="C294" t="n">
-        <v>96.45999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="D294" t="n">
-        <v>29129</v>
+        <v>23355</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>109.01</v>
+        <v>107.57</v>
       </c>
       <c r="B295" t="n">
-        <v>37310</v>
+        <v>32058</v>
       </c>
       <c r="C295" t="n">
-        <v>104.92</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D295" t="n">
-        <v>20575</v>
+        <v>24947</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>112.81</v>
+        <v>108.49</v>
       </c>
       <c r="B296" t="n">
-        <v>25722</v>
+        <v>30908</v>
       </c>
       <c r="C296" t="n">
-        <v>114.16</v>
+        <v>95.5</v>
       </c>
       <c r="D296" t="n">
-        <v>16449</v>
+        <v>19440</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>108.7</v>
+        <v>108.85</v>
       </c>
       <c r="B297" t="n">
-        <v>33010</v>
+        <v>28726</v>
       </c>
       <c r="C297" t="n">
-        <v>106.2</v>
+        <v>108.23</v>
       </c>
       <c r="D297" t="n">
-        <v>28759</v>
+        <v>13385</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>102.02</v>
+        <v>109.33</v>
       </c>
       <c r="B298" t="n">
-        <v>45664</v>
+        <v>27143</v>
       </c>
       <c r="C298" t="n">
-        <v>104.23</v>
+        <v>110.57</v>
       </c>
       <c r="D298" t="n">
-        <v>22966</v>
+        <v>29973</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1.43</v>
+        <v>109.62</v>
       </c>
       <c r="B299" t="n">
-        <v>23845</v>
+        <v>27670</v>
       </c>
       <c r="C299" t="n">
-        <v>1.28</v>
+        <v>126.48</v>
       </c>
       <c r="D299" t="n">
-        <v>20828</v>
+        <v>22327</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>99.61</v>
+        <v>109.78</v>
       </c>
       <c r="B300" t="n">
-        <v>45134</v>
+        <v>26588</v>
       </c>
       <c r="C300" t="n">
-        <v>102.44</v>
+        <v>116.6</v>
       </c>
       <c r="D300" t="n">
-        <v>27585</v>
+        <v>10106</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>90.83</v>
+        <v>110.02</v>
       </c>
       <c r="B301" t="n">
-        <v>26037</v>
+        <v>26903</v>
       </c>
       <c r="C301" t="n">
-        <v>88.89</v>
+        <v>136.21</v>
       </c>
       <c r="D301" t="n">
-        <v>16549</v>
+        <v>29866</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>100.76</v>
+        <v>110.23</v>
       </c>
       <c r="B302" t="n">
-        <v>46028</v>
+        <v>26011</v>
       </c>
       <c r="C302" t="n">
-        <v>101.5</v>
+        <v>106.23</v>
       </c>
       <c r="D302" t="n">
-        <v>12101</v>
+        <v>27313</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>107.06</v>
+        <v>110.28</v>
       </c>
       <c r="B303" t="n">
-        <v>45381</v>
+        <v>25950</v>
       </c>
       <c r="C303" t="n">
-        <v>111.15</v>
+        <v>113.25</v>
       </c>
       <c r="D303" t="n">
-        <v>20532</v>
+        <v>23451</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>98.15000000000001</v>
+        <v>110.54</v>
       </c>
       <c r="B304" t="n">
-        <v>40996</v>
+        <v>25403</v>
       </c>
       <c r="C304" t="n">
-        <v>101.11</v>
+        <v>123.99</v>
       </c>
       <c r="D304" t="n">
-        <v>25706</v>
+        <v>16111</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>108.94</v>
+        <v>111.81</v>
       </c>
       <c r="B305" t="n">
-        <v>35088</v>
+        <v>25455</v>
       </c>
       <c r="C305" t="n">
-        <v>106.79</v>
+        <v>131.37</v>
       </c>
       <c r="D305" t="n">
-        <v>27021</v>
+        <v>13538</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>110.5</v>
+        <v>111.86</v>
       </c>
       <c r="B306" t="n">
-        <v>31068</v>
+        <v>24600</v>
       </c>
       <c r="C306" t="n">
-        <v>111.65</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="D306" t="n">
-        <v>28129</v>
+        <v>25601</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>103.09</v>
+        <v>113.14</v>
       </c>
       <c r="B307" t="n">
-        <v>47720</v>
+        <v>21412</v>
       </c>
       <c r="C307" t="n">
-        <v>100.4</v>
+        <v>104.43</v>
       </c>
       <c r="D307" t="n">
-        <v>14014</v>
+        <v>14313</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>92.5</v>
+        <v>113.24</v>
       </c>
       <c r="B308" t="n">
-        <v>23768</v>
+        <v>21901</v>
       </c>
       <c r="C308" t="n">
-        <v>92.23</v>
+        <v>138</v>
       </c>
       <c r="D308" t="n">
-        <v>20062</v>
+        <v>18735</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>103.13</v>
+        <v>113.27</v>
       </c>
       <c r="B309" t="n">
-        <v>47354</v>
+        <v>21850</v>
       </c>
       <c r="C309" t="n">
-        <v>105.49</v>
+        <v>109.4</v>
       </c>
       <c r="D309" t="n">
-        <v>21758</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>77.7</v>
+        <v>113.39</v>
       </c>
       <c r="B310" t="n">
-        <v>22798</v>
+        <v>21555</v>
       </c>
       <c r="C310" t="n">
-        <v>75.31</v>
+        <v>126.76</v>
       </c>
       <c r="D310" t="n">
-        <v>24600</v>
+        <v>10639</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>107.94</v>
+        <v>113.66</v>
       </c>
       <c r="B311" t="n">
-        <v>38673</v>
+        <v>20993</v>
       </c>
       <c r="C311" t="n">
-        <v>105.97</v>
+        <v>135.94</v>
       </c>
       <c r="D311" t="n">
-        <v>29973</v>
+        <v>29949</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>95.78</v>
+        <v>114.19</v>
       </c>
       <c r="B312" t="n">
-        <v>34808</v>
+        <v>20241</v>
       </c>
       <c r="C312" t="n">
-        <v>99.84999999999999</v>
+        <v>102.89</v>
       </c>
       <c r="D312" t="n">
-        <v>13508</v>
+        <v>26244</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>49.47</v>
+        <v>114.43</v>
       </c>
       <c r="B313" t="n">
-        <v>25368</v>
+        <v>20867</v>
       </c>
       <c r="C313" t="n">
-        <v>48.63</v>
+        <v>96.25</v>
       </c>
       <c r="D313" t="n">
-        <v>23207</v>
+        <v>27322</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>64.64</v>
+        <v>115.9</v>
       </c>
       <c r="B314" t="n">
-        <v>23869</v>
+        <v>21056</v>
       </c>
       <c r="C314" t="n">
-        <v>62.3</v>
+        <v>103.16</v>
       </c>
       <c r="D314" t="n">
-        <v>15677</v>
+        <v>17826</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>110.13</v>
+        <v>116.55</v>
       </c>
       <c r="B315" t="n">
-        <v>27964</v>
+        <v>20224</v>
       </c>
       <c r="C315" t="n">
-        <v>107.59</v>
+        <v>139.78</v>
       </c>
       <c r="D315" t="n">
-        <v>26958</v>
+        <v>22470</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>59.54</v>
+        <v>116.64</v>
       </c>
       <c r="B316" t="n">
-        <v>23529</v>
+        <v>20135</v>
       </c>
       <c r="C316" t="n">
-        <v>57.35</v>
+        <v>101.04</v>
       </c>
       <c r="D316" t="n">
-        <v>11474</v>
+        <v>14978</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>106.58</v>
+        <v>116.77</v>
       </c>
       <c r="B317" t="n">
-        <v>42167</v>
+        <v>21139</v>
       </c>
       <c r="C317" t="n">
-        <v>108.61</v>
+        <v>135.09</v>
       </c>
       <c r="D317" t="n">
-        <v>24603</v>
+        <v>25186</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>150.29</v>
+        <v>116.82</v>
       </c>
       <c r="B318" t="n">
-        <v>21684</v>
+        <v>19373</v>
       </c>
       <c r="C318" t="n">
-        <v>149.06</v>
+        <v>128.3</v>
       </c>
       <c r="D318" t="n">
-        <v>12539</v>
+        <v>29984</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>107.73</v>
+        <v>117.09</v>
       </c>
       <c r="B319" t="n">
-        <v>42662</v>
+        <v>19997</v>
       </c>
       <c r="C319" t="n">
-        <v>111.8</v>
+        <v>104.44</v>
       </c>
       <c r="D319" t="n">
-        <v>21723</v>
+        <v>20244</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>91.48</v>
+        <v>117.55</v>
       </c>
       <c r="B320" t="n">
-        <v>24639</v>
+        <v>19068</v>
       </c>
       <c r="C320" t="n">
-        <v>91.17</v>
+        <v>121.98</v>
       </c>
       <c r="D320" t="n">
-        <v>24273</v>
+        <v>29390</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>107.92</v>
+        <v>117.7</v>
       </c>
       <c r="B321" t="n">
-        <v>38945</v>
+        <v>19787</v>
       </c>
       <c r="C321" t="n">
-        <v>109.72</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="D321" t="n">
-        <v>22027</v>
+        <v>22545</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>102.43</v>
+        <v>117.9</v>
       </c>
       <c r="B322" t="n">
-        <v>48336</v>
+        <v>20614</v>
       </c>
       <c r="C322" t="n">
-        <v>103.84</v>
+        <v>110.77</v>
       </c>
       <c r="D322" t="n">
-        <v>12881</v>
+        <v>25685</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>101.01</v>
+        <v>117.98</v>
       </c>
       <c r="B323" t="n">
-        <v>47692</v>
+        <v>19703</v>
       </c>
       <c r="C323" t="n">
-        <v>99.14</v>
+        <v>124.94</v>
       </c>
       <c r="D323" t="n">
-        <v>16532</v>
+        <v>26556</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>94.48</v>
+        <v>118.3</v>
       </c>
       <c r="B324" t="n">
-        <v>33649</v>
+        <v>19822</v>
       </c>
       <c r="C324" t="n">
-        <v>97.45</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="D324" t="n">
-        <v>29195</v>
+        <v>24511</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>111.09</v>
+        <v>118.62</v>
       </c>
       <c r="B325" t="n">
-        <v>32317</v>
+        <v>19976</v>
       </c>
       <c r="C325" t="n">
-        <v>109.05</v>
+        <v>106.47</v>
       </c>
       <c r="D325" t="n">
-        <v>16426</v>
+        <v>19280</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>103.09</v>
+        <v>119.28</v>
       </c>
       <c r="B326" t="n">
-        <v>46600</v>
+        <v>19683</v>
       </c>
       <c r="C326" t="n">
-        <v>100.44</v>
+        <v>127.19</v>
       </c>
       <c r="D326" t="n">
-        <v>27439</v>
+        <v>26426</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>107.37</v>
+        <v>119.78</v>
       </c>
       <c r="B327" t="n">
-        <v>39762</v>
+        <v>20432</v>
       </c>
       <c r="C327" t="n">
-        <v>105.52</v>
+        <v>99.03</v>
       </c>
       <c r="D327" t="n">
-        <v>27185</v>
+        <v>13212</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>36.47</v>
+        <v>119.79</v>
       </c>
       <c r="B328" t="n">
-        <v>21120</v>
+        <v>19711</v>
       </c>
       <c r="C328" t="n">
-        <v>36.83</v>
+        <v>131.68</v>
       </c>
       <c r="D328" t="n">
-        <v>17405</v>
+        <v>17833</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>101.49</v>
+        <v>119.95</v>
       </c>
       <c r="B329" t="n">
-        <v>47217</v>
+        <v>19610</v>
       </c>
       <c r="C329" t="n">
-        <v>105.21</v>
+        <v>140.4</v>
       </c>
       <c r="D329" t="n">
-        <v>22804</v>
+        <v>24516</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>105.83</v>
+        <v>120.17</v>
       </c>
       <c r="B330" t="n">
-        <v>43432</v>
+        <v>20307</v>
       </c>
       <c r="C330" t="n">
-        <v>110.24</v>
+        <v>119.43</v>
       </c>
       <c r="D330" t="n">
-        <v>18326</v>
+        <v>24933</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>111.94</v>
+        <v>120.57</v>
       </c>
       <c r="B331" t="n">
-        <v>26065</v>
+        <v>19114</v>
       </c>
       <c r="C331" t="n">
-        <v>110.8</v>
+        <v>104.62</v>
       </c>
       <c r="D331" t="n">
-        <v>26186</v>
+        <v>10672</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>54.96</v>
+        <v>120.93</v>
       </c>
       <c r="B332" t="n">
-        <v>24798</v>
+        <v>19797</v>
       </c>
       <c r="C332" t="n">
-        <v>55.15</v>
+        <v>99.72</v>
       </c>
       <c r="D332" t="n">
-        <v>16702</v>
+        <v>27561</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>38.37</v>
+        <v>121.02</v>
       </c>
       <c r="B333" t="n">
-        <v>23304</v>
+        <v>18692</v>
       </c>
       <c r="C333" t="n">
-        <v>38.79</v>
+        <v>105.64</v>
       </c>
       <c r="D333" t="n">
-        <v>22563</v>
+        <v>13656</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>108.37</v>
+        <v>121.4</v>
       </c>
       <c r="B334" t="n">
-        <v>34222</v>
+        <v>20471</v>
       </c>
       <c r="C334" t="n">
-        <v>110.34</v>
+        <v>153.77</v>
       </c>
       <c r="D334" t="n">
-        <v>15335</v>
+        <v>18715</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>94.89</v>
+        <v>121.42</v>
       </c>
       <c r="B335" t="n">
-        <v>32588</v>
+        <v>18318</v>
       </c>
       <c r="C335" t="n">
-        <v>92.06999999999999</v>
+        <v>123.42</v>
       </c>
       <c r="D335" t="n">
-        <v>24966</v>
+        <v>29951</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>101.18</v>
+        <v>121.51</v>
       </c>
       <c r="B336" t="n">
-        <v>48703</v>
+        <v>21518</v>
       </c>
       <c r="C336" t="n">
-        <v>102.33</v>
+        <v>135.36</v>
       </c>
       <c r="D336" t="n">
-        <v>24526</v>
+        <v>26792</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>102.11</v>
+        <v>121.65</v>
       </c>
       <c r="B337" t="n">
-        <v>51696</v>
+        <v>19835</v>
       </c>
       <c r="C337" t="n">
-        <v>100.85</v>
+        <v>135.4</v>
       </c>
       <c r="D337" t="n">
-        <v>19931</v>
+        <v>14974</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>101.23</v>
+        <v>122.92</v>
       </c>
       <c r="B338" t="n">
-        <v>45959</v>
+        <v>18862</v>
       </c>
       <c r="C338" t="n">
-        <v>99.18000000000001</v>
+        <v>113.04</v>
       </c>
       <c r="D338" t="n">
-        <v>14498</v>
+        <v>18430</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>96.48</v>
+        <v>123.67</v>
       </c>
       <c r="B339" t="n">
-        <v>39942</v>
+        <v>21468</v>
       </c>
       <c r="C339" t="n">
-        <v>98</v>
+        <v>110.1</v>
       </c>
       <c r="D339" t="n">
-        <v>12371</v>
+        <v>14314</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>102.01</v>
+        <v>124.09</v>
       </c>
       <c r="B340" t="n">
-        <v>49344</v>
+        <v>19133</v>
       </c>
       <c r="C340" t="n">
-        <v>100.26</v>
+        <v>141.88</v>
       </c>
       <c r="D340" t="n">
-        <v>20829</v>
+        <v>10906</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>95.33</v>
+        <v>124.73</v>
       </c>
       <c r="B341" t="n">
-        <v>33853</v>
+        <v>19251</v>
       </c>
       <c r="C341" t="n">
-        <v>96.23</v>
+        <v>140.87</v>
       </c>
       <c r="D341" t="n">
-        <v>25576</v>
+        <v>25856</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>96.02</v>
+        <v>125.83</v>
       </c>
       <c r="B342" t="n">
-        <v>34189</v>
+        <v>20425</v>
       </c>
       <c r="C342" t="n">
-        <v>91.75</v>
+        <v>118.91</v>
       </c>
       <c r="D342" t="n">
-        <v>20092</v>
+        <v>29410</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>99.94</v>
+        <v>126.41</v>
       </c>
       <c r="B343" t="n">
-        <v>43806</v>
+        <v>18560</v>
       </c>
       <c r="C343" t="n">
-        <v>97.73999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="D343" t="n">
-        <v>22850</v>
+        <v>14226</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>90.29000000000001</v>
+        <v>126.97</v>
       </c>
       <c r="B344" t="n">
-        <v>23531</v>
+        <v>19474</v>
       </c>
       <c r="C344" t="n">
-        <v>88.69</v>
+        <v>102.34</v>
       </c>
       <c r="D344" t="n">
-        <v>24583</v>
+        <v>28474</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>47.92</v>
+        <v>127.3</v>
       </c>
       <c r="B345" t="n">
-        <v>25079</v>
+        <v>19002</v>
       </c>
       <c r="C345" t="n">
-        <v>50.24</v>
+        <v>111.07</v>
       </c>
       <c r="D345" t="n">
-        <v>16320</v>
+        <v>21162</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>91.38</v>
+        <v>127.56</v>
       </c>
       <c r="B346" t="n">
-        <v>23671</v>
+        <v>17873</v>
       </c>
       <c r="C346" t="n">
-        <v>91.14</v>
+        <v>152.35</v>
       </c>
       <c r="D346" t="n">
-        <v>23036</v>
+        <v>22313</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>99.38</v>
+        <v>127.65</v>
       </c>
       <c r="B347" t="n">
-        <v>44027</v>
+        <v>20333</v>
       </c>
       <c r="C347" t="n">
-        <v>98.34</v>
+        <v>112.15</v>
       </c>
       <c r="D347" t="n">
-        <v>24131</v>
+        <v>16817</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>107.75</v>
+        <v>127.9</v>
       </c>
       <c r="B348" t="n">
-        <v>36587</v>
+        <v>20220</v>
       </c>
       <c r="C348" t="n">
-        <v>104.78</v>
+        <v>143.74</v>
       </c>
       <c r="D348" t="n">
-        <v>25688</v>
+        <v>11914</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>93.01000000000001</v>
+        <v>128.17</v>
       </c>
       <c r="B349" t="n">
-        <v>26815</v>
+        <v>20052</v>
       </c>
       <c r="C349" t="n">
-        <v>94.75</v>
+        <v>139.28</v>
       </c>
       <c r="D349" t="n">
-        <v>15995</v>
+        <v>17575</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>158.82</v>
+        <v>128.54</v>
       </c>
       <c r="B350" t="n">
-        <v>23137</v>
+        <v>20665</v>
       </c>
       <c r="C350" t="n">
-        <v>155.83</v>
+        <v>123.95</v>
       </c>
       <c r="D350" t="n">
-        <v>25674</v>
+        <v>26036</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>92.20999999999999</v>
+        <v>128.79</v>
       </c>
       <c r="B351" t="n">
-        <v>27379</v>
+        <v>20201</v>
       </c>
       <c r="C351" t="n">
-        <v>94.7</v>
+        <v>122.24</v>
       </c>
       <c r="D351" t="n">
-        <v>23268</v>
+        <v>29446</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>121.07</v>
+        <v>128.97</v>
       </c>
       <c r="B352" t="n">
-        <v>21904</v>
+        <v>20792</v>
       </c>
       <c r="C352" t="n">
-        <v>117.11</v>
+        <v>111.53</v>
       </c>
       <c r="D352" t="n">
-        <v>20397</v>
+        <v>15968</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>112.85</v>
+        <v>129.26</v>
       </c>
       <c r="B353" t="n">
-        <v>24807</v>
+        <v>22513</v>
       </c>
       <c r="C353" t="n">
-        <v>110.39</v>
+        <v>143.87</v>
       </c>
       <c r="D353" t="n">
-        <v>20284</v>
+        <v>25712</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>94.88</v>
+        <v>129.38</v>
       </c>
       <c r="B354" t="n">
-        <v>34281</v>
+        <v>18947</v>
       </c>
       <c r="C354" t="n">
-        <v>96.37</v>
+        <v>142.89</v>
       </c>
       <c r="D354" t="n">
-        <v>11150</v>
+        <v>10345</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>109.13</v>
+        <v>129.4</v>
       </c>
       <c r="B355" t="n">
-        <v>35606</v>
+        <v>18775</v>
       </c>
       <c r="C355" t="n">
-        <v>112.02</v>
+        <v>106.16</v>
       </c>
       <c r="D355" t="n">
-        <v>27578</v>
+        <v>14788</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>99.73</v>
+        <v>129.73</v>
       </c>
       <c r="B356" t="n">
-        <v>42645</v>
+        <v>19251</v>
       </c>
       <c r="C356" t="n">
-        <v>101.54</v>
+        <v>111.31</v>
       </c>
       <c r="D356" t="n">
-        <v>19303</v>
+        <v>15172</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>96.47</v>
+        <v>129.81</v>
       </c>
       <c r="B357" t="n">
-        <v>35903</v>
+        <v>18747</v>
       </c>
       <c r="C357" t="n">
-        <v>97.43000000000001</v>
+        <v>141.69</v>
       </c>
       <c r="D357" t="n">
-        <v>12666</v>
+        <v>21847</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>114.22</v>
+        <v>129.91</v>
       </c>
       <c r="B358" t="n">
-        <v>23730</v>
+        <v>19027</v>
       </c>
       <c r="C358" t="n">
-        <v>119.21</v>
+        <v>131.21</v>
       </c>
       <c r="D358" t="n">
-        <v>13112</v>
+        <v>16369</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>36.27</v>
+        <v>130.44</v>
       </c>
       <c r="B359" t="n">
-        <v>24952</v>
+        <v>19361</v>
       </c>
       <c r="C359" t="n">
-        <v>35.12</v>
+        <v>112.81</v>
       </c>
       <c r="D359" t="n">
-        <v>10135</v>
+        <v>17218</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>90.25</v>
+        <v>130.9</v>
       </c>
       <c r="B360" t="n">
-        <v>24100</v>
+        <v>18440</v>
       </c>
       <c r="C360" t="n">
-        <v>92.55</v>
+        <v>118.96</v>
       </c>
       <c r="D360" t="n">
-        <v>22436</v>
+        <v>21135</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>112.39</v>
+        <v>131.18</v>
       </c>
       <c r="B361" t="n">
-        <v>24427</v>
+        <v>20140</v>
       </c>
       <c r="C361" t="n">
-        <v>114.55</v>
+        <v>125.66</v>
       </c>
       <c r="D361" t="n">
-        <v>19773</v>
+        <v>12571</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>105.49</v>
+        <v>131.33</v>
       </c>
       <c r="B362" t="n">
-        <v>45400</v>
+        <v>20352</v>
       </c>
       <c r="C362" t="n">
-        <v>104.7</v>
+        <v>143.95</v>
       </c>
       <c r="D362" t="n">
-        <v>26830</v>
+        <v>20629</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>111.01</v>
+        <v>131.55</v>
       </c>
       <c r="B363" t="n">
-        <v>29639</v>
+        <v>20519</v>
       </c>
       <c r="C363" t="n">
-        <v>111.24</v>
+        <v>116.91</v>
       </c>
       <c r="D363" t="n">
-        <v>13322</v>
+        <v>12422</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>113.16</v>
+        <v>132.09</v>
       </c>
       <c r="B364" t="n">
-        <v>26206</v>
+        <v>19788</v>
       </c>
       <c r="C364" t="n">
-        <v>110.26</v>
+        <v>136.45</v>
       </c>
       <c r="D364" t="n">
-        <v>15554</v>
+        <v>25001</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>113.17</v>
+        <v>132.19</v>
       </c>
       <c r="B365" t="n">
-        <v>25676</v>
+        <v>18873</v>
       </c>
       <c r="C365" t="n">
-        <v>115.38</v>
+        <v>109.67</v>
       </c>
       <c r="D365" t="n">
-        <v>23009</v>
+        <v>24637</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>99.52</v>
+        <v>132.24</v>
       </c>
       <c r="B366" t="n">
-        <v>42882</v>
+        <v>18827</v>
       </c>
       <c r="C366" t="n">
-        <v>102.86</v>
+        <v>118.58</v>
       </c>
       <c r="D366" t="n">
-        <v>21061</v>
+        <v>24139</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>108.1</v>
+        <v>132.44</v>
       </c>
       <c r="B367" t="n">
-        <v>41433</v>
+        <v>20478</v>
       </c>
       <c r="C367" t="n">
-        <v>110.69</v>
+        <v>114.64</v>
       </c>
       <c r="D367" t="n">
-        <v>25941</v>
+        <v>21543</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>92.45999999999999</v>
+        <v>132.45</v>
       </c>
       <c r="B368" t="n">
-        <v>28505</v>
+        <v>21779</v>
       </c>
       <c r="C368" t="n">
-        <v>92.45</v>
+        <v>124.28</v>
       </c>
       <c r="D368" t="n">
-        <v>24747</v>
+        <v>13262</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>114.08</v>
+        <v>133.34</v>
       </c>
       <c r="B369" t="n">
-        <v>23229</v>
+        <v>20039</v>
       </c>
       <c r="C369" t="n">
-        <v>115.41</v>
+        <v>117.81</v>
       </c>
       <c r="D369" t="n">
-        <v>20879</v>
+        <v>27830</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>94.44</v>
+        <v>133.81</v>
       </c>
       <c r="B370" t="n">
-        <v>32073</v>
+        <v>18283</v>
       </c>
       <c r="C370" t="n">
-        <v>97.81</v>
+        <v>157.07</v>
       </c>
       <c r="D370" t="n">
-        <v>16989</v>
+        <v>29222</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>100.53</v>
+        <v>133.9</v>
       </c>
       <c r="B371" t="n">
-        <v>43914</v>
+        <v>18622</v>
       </c>
       <c r="C371" t="n">
-        <v>102.49</v>
+        <v>160.13</v>
       </c>
       <c r="D371" t="n">
-        <v>22030</v>
+        <v>16707</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>105.13</v>
+        <v>135.08</v>
       </c>
       <c r="B372" t="n">
-        <v>45811</v>
+        <v>18143</v>
       </c>
       <c r="C372" t="n">
-        <v>105.26</v>
+        <v>125.52</v>
       </c>
       <c r="D372" t="n">
-        <v>10895</v>
+        <v>18123</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>93.5</v>
+        <v>135.37</v>
       </c>
       <c r="B373" t="n">
-        <v>28254</v>
+        <v>19968</v>
       </c>
       <c r="C373" t="n">
-        <v>91.58</v>
+        <v>133.6</v>
       </c>
       <c r="D373" t="n">
-        <v>14009</v>
+        <v>27805</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>107.05</v>
+        <v>135.39</v>
       </c>
       <c r="B374" t="n">
-        <v>41837</v>
+        <v>18033</v>
       </c>
       <c r="C374" t="n">
-        <v>106.66</v>
+        <v>133.68</v>
       </c>
       <c r="D374" t="n">
-        <v>14175</v>
+        <v>22957</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>97.77</v>
+        <v>136.21</v>
       </c>
       <c r="B375" t="n">
-        <v>42617</v>
+        <v>22102</v>
       </c>
       <c r="C375" t="n">
-        <v>96.94</v>
+        <v>120.02</v>
       </c>
       <c r="D375" t="n">
-        <v>20634</v>
+        <v>24010</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>113.04</v>
+        <v>136.54</v>
       </c>
       <c r="B376" t="n">
-        <v>26384</v>
+        <v>19996</v>
       </c>
       <c r="C376" t="n">
-        <v>109.16</v>
+        <v>131.15</v>
       </c>
       <c r="D376" t="n">
-        <v>29414</v>
+        <v>22764</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>99.41</v>
+        <v>136.73</v>
       </c>
       <c r="B377" t="n">
-        <v>47282</v>
+        <v>18011</v>
       </c>
       <c r="C377" t="n">
-        <v>95.17</v>
+        <v>158.9</v>
       </c>
       <c r="D377" t="n">
-        <v>11350</v>
+        <v>20102</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>106.55</v>
+        <v>136.92</v>
       </c>
       <c r="B378" t="n">
-        <v>44033</v>
+        <v>16793</v>
       </c>
       <c r="C378" t="n">
-        <v>107.8</v>
+        <v>155.8</v>
       </c>
       <c r="D378" t="n">
-        <v>29319</v>
+        <v>20409</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>53.66</v>
+        <v>137.63</v>
       </c>
       <c r="B379" t="n">
-        <v>23966</v>
+        <v>20680</v>
       </c>
       <c r="C379" t="n">
-        <v>54.14</v>
+        <v>149.91</v>
       </c>
       <c r="D379" t="n">
-        <v>10230</v>
+        <v>23091</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>132.54</v>
+        <v>137.73</v>
       </c>
       <c r="B380" t="n">
-        <v>20890</v>
+        <v>20237</v>
       </c>
       <c r="C380" t="n">
-        <v>135.87</v>
+        <v>102.54</v>
       </c>
       <c r="D380" t="n">
-        <v>21751</v>
+        <v>24283</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>101.97</v>
+        <v>137.99</v>
       </c>
       <c r="B381" t="n">
-        <v>46613</v>
+        <v>19422</v>
       </c>
       <c r="C381" t="n">
-        <v>104.86</v>
+        <v>140.86</v>
       </c>
       <c r="D381" t="n">
-        <v>18085</v>
+        <v>16410</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>23.31</v>
+        <v>138.35</v>
       </c>
       <c r="B382" t="n">
-        <v>25066</v>
+        <v>19198</v>
       </c>
       <c r="C382" t="n">
-        <v>22.04</v>
+        <v>117.86</v>
       </c>
       <c r="D382" t="n">
-        <v>20279</v>
+        <v>24283</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>43.92</v>
+        <v>138.62</v>
       </c>
       <c r="B383" t="n">
-        <v>22687</v>
+        <v>17495</v>
       </c>
       <c r="C383" t="n">
-        <v>43.47</v>
+        <v>153.39</v>
       </c>
       <c r="D383" t="n">
-        <v>24932</v>
+        <v>20842</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>93.28</v>
+        <v>138.7</v>
       </c>
       <c r="B384" t="n">
-        <v>25263</v>
+        <v>19600</v>
       </c>
       <c r="C384" t="n">
-        <v>91.94</v>
+        <v>129.84</v>
       </c>
       <c r="D384" t="n">
-        <v>23034</v>
+        <v>21615</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>99.33</v>
+        <v>140.02</v>
       </c>
       <c r="B385" t="n">
-        <v>45705</v>
+        <v>19110</v>
       </c>
       <c r="C385" t="n">
-        <v>101.28</v>
+        <v>143.97</v>
       </c>
       <c r="D385" t="n">
-        <v>24050</v>
+        <v>22960</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>100.93</v>
+        <v>140.87</v>
       </c>
       <c r="B386" t="n">
-        <v>45311</v>
+        <v>16747</v>
       </c>
       <c r="C386" t="n">
-        <v>98.5</v>
+        <v>162.82</v>
       </c>
       <c r="D386" t="n">
-        <v>25316</v>
+        <v>19073</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>106.38</v>
+        <v>141.45</v>
       </c>
       <c r="B387" t="n">
-        <v>39135</v>
+        <v>19522</v>
       </c>
       <c r="C387" t="n">
-        <v>107.7</v>
+        <v>141.75</v>
       </c>
       <c r="D387" t="n">
-        <v>22275</v>
+        <v>20251</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>101.39</v>
+        <v>142.26</v>
       </c>
       <c r="B388" t="n">
-        <v>46877</v>
+        <v>18248</v>
       </c>
       <c r="C388" t="n">
-        <v>103.59</v>
+        <v>127.66</v>
       </c>
       <c r="D388" t="n">
-        <v>13702</v>
+        <v>22962</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>94.75</v>
+        <v>143.43</v>
       </c>
       <c r="B389" t="n">
-        <v>33569</v>
+        <v>20082</v>
       </c>
       <c r="C389" t="n">
-        <v>97.12</v>
+        <v>155.13</v>
       </c>
       <c r="D389" t="n">
-        <v>13946</v>
+        <v>10207</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>96.81999999999999</v>
+        <v>144.28</v>
       </c>
       <c r="B390" t="n">
-        <v>35923</v>
+        <v>22222</v>
       </c>
       <c r="C390" t="n">
-        <v>99.39</v>
+        <v>155.76</v>
       </c>
       <c r="D390" t="n">
-        <v>25819</v>
+        <v>24886</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>103.83</v>
+        <v>144.45</v>
       </c>
       <c r="B391" t="n">
-        <v>43469</v>
+        <v>21410</v>
       </c>
       <c r="C391" t="n">
-        <v>107.95</v>
+        <v>112.16</v>
       </c>
       <c r="D391" t="n">
-        <v>18667</v>
+        <v>13518</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>102.38</v>
+        <v>144.78</v>
       </c>
       <c r="B392" t="n">
-        <v>45760</v>
+        <v>23201</v>
       </c>
       <c r="C392" t="n">
-        <v>99.02</v>
+        <v>152.65</v>
       </c>
       <c r="D392" t="n">
-        <v>24994</v>
+        <v>17574</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>137.48</v>
+        <v>145.09</v>
       </c>
       <c r="B393" t="n">
-        <v>21417</v>
+        <v>19489</v>
       </c>
       <c r="C393" t="n">
-        <v>135.85</v>
+        <v>151.77</v>
       </c>
       <c r="D393" t="n">
-        <v>13271</v>
+        <v>19059</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>159.91</v>
+        <v>145.14</v>
       </c>
       <c r="B394" t="n">
-        <v>21819</v>
+        <v>20401</v>
       </c>
       <c r="C394" t="n">
-        <v>162.57</v>
+        <v>164.13</v>
       </c>
       <c r="D394" t="n">
-        <v>14412</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>101.64</v>
+        <v>145.37</v>
       </c>
       <c r="B395" t="n">
-        <v>47591</v>
+        <v>21562</v>
       </c>
       <c r="C395" t="n">
-        <v>103.17</v>
+        <v>145.77</v>
       </c>
       <c r="D395" t="n">
-        <v>28718</v>
+        <v>10279</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>92.98999999999999</v>
+        <v>145.47</v>
       </c>
       <c r="B396" t="n">
-        <v>29259</v>
+        <v>19732</v>
       </c>
       <c r="C396" t="n">
-        <v>90.34999999999999</v>
+        <v>151.31</v>
       </c>
       <c r="D396" t="n">
-        <v>26336</v>
+        <v>14716</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>101.4</v>
+        <v>145.68</v>
       </c>
       <c r="B397" t="n">
-        <v>45510</v>
+        <v>21556</v>
       </c>
       <c r="C397" t="n">
-        <v>97.8</v>
+        <v>153.52</v>
       </c>
       <c r="D397" t="n">
-        <v>17106</v>
+        <v>17475</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>166.1</v>
+        <v>145.76</v>
       </c>
       <c r="B398" t="n">
-        <v>25426</v>
+        <v>20459</v>
       </c>
       <c r="C398" t="n">
-        <v>171.01</v>
+        <v>116.37</v>
       </c>
       <c r="D398" t="n">
-        <v>14881</v>
+        <v>27102</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>174.18</v>
+        <v>146.54</v>
       </c>
       <c r="B399" t="n">
-        <v>22146</v>
+        <v>23517</v>
       </c>
       <c r="C399" t="n">
-        <v>168.89</v>
+        <v>152.99</v>
       </c>
       <c r="D399" t="n">
-        <v>13197</v>
+        <v>18346</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>91.16</v>
+        <v>146.68</v>
       </c>
       <c r="B400" t="n">
-        <v>23865</v>
+        <v>20531</v>
       </c>
       <c r="C400" t="n">
-        <v>90.56</v>
+        <v>119.3</v>
       </c>
       <c r="D400" t="n">
-        <v>15086</v>
+        <v>17415</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>97.28</v>
+        <v>147.05</v>
       </c>
       <c r="B401" t="n">
-        <v>39640</v>
+        <v>20607</v>
       </c>
       <c r="C401" t="n">
-        <v>98.98</v>
+        <v>152.36</v>
       </c>
       <c r="D401" t="n">
-        <v>20396</v>
+        <v>16221</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>104.11</v>
+        <v>147.25</v>
       </c>
       <c r="B402" t="n">
-        <v>49857</v>
+        <v>21158</v>
       </c>
       <c r="C402" t="n">
-        <v>105.19</v>
+        <v>151.45</v>
       </c>
       <c r="D402" t="n">
-        <v>25314</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>114.49</v>
+        <v>147.86</v>
       </c>
       <c r="B403" t="n">
-        <v>20467</v>
+        <v>21078</v>
       </c>
       <c r="C403" t="n">
-        <v>109.49</v>
+        <v>118.42</v>
       </c>
       <c r="D403" t="n">
-        <v>27891</v>
+        <v>29438</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>100.47</v>
+        <v>149.12</v>
       </c>
       <c r="B404" t="n">
-        <v>44382</v>
+        <v>23238</v>
       </c>
       <c r="C404" t="n">
-        <v>96.77</v>
+        <v>168.66</v>
       </c>
       <c r="D404" t="n">
-        <v>29141</v>
+        <v>19958</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>98.43000000000001</v>
+        <v>149.33</v>
       </c>
       <c r="B405" t="n">
-        <v>41028</v>
+        <v>22984</v>
       </c>
       <c r="C405" t="n">
-        <v>97.97</v>
+        <v>149.13</v>
       </c>
       <c r="D405" t="n">
-        <v>29281</v>
+        <v>15898</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>112.25</v>
+        <v>149.63</v>
       </c>
       <c r="B406" t="n">
-        <v>26043</v>
+        <v>21415</v>
       </c>
       <c r="C406" t="n">
-        <v>114.29</v>
+        <v>152.74</v>
       </c>
       <c r="D406" t="n">
-        <v>22918</v>
+        <v>28468</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>102.29</v>
+        <v>149.88</v>
       </c>
       <c r="B407" t="n">
-        <v>47447</v>
+        <v>23054</v>
       </c>
       <c r="C407" t="n">
-        <v>101.25</v>
+        <v>130.28</v>
       </c>
       <c r="D407" t="n">
-        <v>26909</v>
+        <v>19620</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>100.67</v>
+        <v>149.94</v>
       </c>
       <c r="B408" t="n">
-        <v>46337</v>
+        <v>25190</v>
       </c>
       <c r="C408" t="n">
-        <v>98.04000000000001</v>
+        <v>148.54</v>
       </c>
       <c r="D408" t="n">
-        <v>13701</v>
+        <v>17265</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>91.90000000000001</v>
+        <v>150.12</v>
       </c>
       <c r="B409" t="n">
-        <v>25576</v>
+        <v>24432</v>
       </c>
       <c r="C409" t="n">
-        <v>94.44</v>
+        <v>128.17</v>
       </c>
       <c r="D409" t="n">
-        <v>25763</v>
+        <v>29283</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>108.63</v>
+        <v>150.45</v>
       </c>
       <c r="B410" t="n">
-        <v>40227</v>
+        <v>24668</v>
       </c>
       <c r="C410" t="n">
-        <v>110.37</v>
+        <v>151.74</v>
       </c>
       <c r="D410" t="n">
-        <v>20423</v>
+        <v>27208</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>95.11</v>
+        <v>150.46</v>
       </c>
       <c r="B411" t="n">
-        <v>31736</v>
+        <v>24147</v>
       </c>
       <c r="C411" t="n">
-        <v>96.92</v>
+        <v>123.63</v>
       </c>
       <c r="D411" t="n">
-        <v>24097</v>
+        <v>26825</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>111.61</v>
+        <v>150.89</v>
       </c>
       <c r="B412" t="n">
-        <v>28318</v>
+        <v>24041</v>
       </c>
       <c r="C412" t="n">
-        <v>109.32</v>
+        <v>161.08</v>
       </c>
       <c r="D412" t="n">
-        <v>11026</v>
+        <v>18298</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>95.29000000000001</v>
+        <v>151.31</v>
       </c>
       <c r="B413" t="n">
-        <v>36533</v>
+        <v>24618</v>
       </c>
       <c r="C413" t="n">
-        <v>98.31</v>
+        <v>151.54</v>
       </c>
       <c r="D413" t="n">
-        <v>18857</v>
+        <v>25197</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>16.57</v>
+        <v>151.36</v>
       </c>
       <c r="B414" t="n">
-        <v>25147</v>
+        <v>24926</v>
       </c>
       <c r="C414" t="n">
-        <v>16.29</v>
+        <v>158.92</v>
       </c>
       <c r="D414" t="n">
-        <v>23959</v>
+        <v>25680</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>105.4</v>
+        <v>151.67</v>
       </c>
       <c r="B415" t="n">
-        <v>42987</v>
+        <v>26338</v>
       </c>
       <c r="C415" t="n">
-        <v>101.46</v>
+        <v>172.14</v>
       </c>
       <c r="D415" t="n">
-        <v>13340</v>
+        <v>25497</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>95.98999999999999</v>
+        <v>151.94</v>
       </c>
       <c r="B416" t="n">
-        <v>37448</v>
+        <v>27742</v>
       </c>
       <c r="C416" t="n">
-        <v>91.86</v>
+        <v>180</v>
       </c>
       <c r="D416" t="n">
-        <v>17241</v>
+        <v>17598</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>102.48</v>
+        <v>152.21</v>
       </c>
       <c r="B417" t="n">
-        <v>48197</v>
+        <v>24575</v>
       </c>
       <c r="C417" t="n">
-        <v>104.8</v>
+        <v>155.39</v>
       </c>
       <c r="D417" t="n">
-        <v>27058</v>
+        <v>14161</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>114.09</v>
+        <v>152.54</v>
       </c>
       <c r="B418" t="n">
-        <v>24645</v>
+        <v>27759</v>
       </c>
       <c r="C418" t="n">
-        <v>118.29</v>
+        <v>180</v>
       </c>
       <c r="D418" t="n">
-        <v>28781</v>
+        <v>20659</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>99.27</v>
+        <v>152.79</v>
       </c>
       <c r="B419" t="n">
-        <v>45101</v>
+        <v>22591</v>
       </c>
       <c r="C419" t="n">
-        <v>96.92</v>
+        <v>180</v>
       </c>
       <c r="D419" t="n">
-        <v>24036</v>
+        <v>11350</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>97.20999999999999</v>
+        <v>152.85</v>
       </c>
       <c r="B420" t="n">
-        <v>43658</v>
+        <v>25269</v>
       </c>
       <c r="C420" t="n">
-        <v>100.63</v>
+        <v>148.6</v>
       </c>
       <c r="D420" t="n">
-        <v>26482</v>
+        <v>16440</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>108.66</v>
+        <v>153</v>
       </c>
       <c r="B421" t="n">
-        <v>36168</v>
+        <v>26221</v>
       </c>
       <c r="C421" t="n">
-        <v>104.88</v>
+        <v>146.67</v>
       </c>
       <c r="D421" t="n">
-        <v>12062</v>
+        <v>20736</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>109.98</v>
+        <v>153.15</v>
       </c>
       <c r="B422" t="n">
-        <v>35151</v>
+        <v>30558</v>
       </c>
       <c r="C422" t="n">
-        <v>105.18</v>
+        <v>141.42</v>
       </c>
       <c r="D422" t="n">
-        <v>25429</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>35.34</v>
+        <v>153.33</v>
       </c>
       <c r="B423" t="n">
-        <v>24074</v>
+        <v>29200</v>
       </c>
       <c r="C423" t="n">
-        <v>33.85</v>
+        <v>155.79</v>
       </c>
       <c r="D423" t="n">
-        <v>11737</v>
+        <v>23325</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>110.21</v>
+        <v>153.44</v>
       </c>
       <c r="B424" t="n">
-        <v>31555</v>
+        <v>25895</v>
       </c>
       <c r="C424" t="n">
-        <v>110.26</v>
+        <v>171.6</v>
       </c>
       <c r="D424" t="n">
-        <v>18438</v>
+        <v>14619</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>95.73999999999999</v>
+        <v>153.57</v>
       </c>
       <c r="B425" t="n">
-        <v>34699</v>
+        <v>27316</v>
       </c>
       <c r="C425" t="n">
-        <v>96.90000000000001</v>
+        <v>144.19</v>
       </c>
       <c r="D425" t="n">
-        <v>24976</v>
+        <v>25160</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>108.39</v>
+        <v>153.57</v>
       </c>
       <c r="B426" t="n">
-        <v>37891</v>
+        <v>25749</v>
       </c>
       <c r="C426" t="n">
-        <v>109.99</v>
+        <v>133.52</v>
       </c>
       <c r="D426" t="n">
-        <v>21802</v>
+        <v>29095</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>95.59999999999999</v>
+        <v>154</v>
       </c>
       <c r="B427" t="n">
-        <v>36157</v>
+        <v>27750</v>
       </c>
       <c r="C427" t="n">
-        <v>93.06999999999999</v>
+        <v>132.27</v>
       </c>
       <c r="D427" t="n">
-        <v>19925</v>
+        <v>13117</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>112.43</v>
+        <v>154.01</v>
       </c>
       <c r="B428" t="n">
-        <v>27918</v>
+        <v>29370</v>
       </c>
       <c r="C428" t="n">
-        <v>116.94</v>
+        <v>134.03</v>
       </c>
       <c r="D428" t="n">
-        <v>22020</v>
+        <v>13392</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>106.93</v>
+        <v>154.1</v>
       </c>
       <c r="B429" t="n">
-        <v>42092</v>
+        <v>26939</v>
       </c>
       <c r="C429" t="n">
-        <v>104.83</v>
+        <v>180</v>
       </c>
       <c r="D429" t="n">
-        <v>10214</v>
+        <v>27282</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>96.56</v>
+        <v>154.25</v>
       </c>
       <c r="B430" t="n">
-        <v>35681</v>
+        <v>26889</v>
       </c>
       <c r="C430" t="n">
-        <v>94.13</v>
+        <v>131.8</v>
       </c>
       <c r="D430" t="n">
-        <v>12931</v>
+        <v>22343</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>100.14</v>
+        <v>154.43</v>
       </c>
       <c r="B431" t="n">
-        <v>45276</v>
+        <v>27272</v>
       </c>
       <c r="C431" t="n">
-        <v>102.11</v>
+        <v>140.58</v>
       </c>
       <c r="D431" t="n">
-        <v>27414</v>
+        <v>24692</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>105.24</v>
+        <v>154.92</v>
       </c>
       <c r="B432" t="n">
-        <v>49117</v>
+        <v>28642</v>
       </c>
       <c r="C432" t="n">
-        <v>103.38</v>
+        <v>170.06</v>
       </c>
       <c r="D432" t="n">
-        <v>16524</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>98.34999999999999</v>
+        <v>154.92</v>
       </c>
       <c r="B433" t="n">
-        <v>38900</v>
+        <v>29127</v>
       </c>
       <c r="C433" t="n">
-        <v>100.52</v>
+        <v>120.76</v>
       </c>
       <c r="D433" t="n">
-        <v>29383</v>
+        <v>23741</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>111.47</v>
+        <v>155.04</v>
       </c>
       <c r="B434" t="n">
-        <v>29969</v>
+        <v>27723</v>
       </c>
       <c r="C434" t="n">
-        <v>108.44</v>
+        <v>144.44</v>
       </c>
       <c r="D434" t="n">
-        <v>19796</v>
+        <v>28069</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>96.58</v>
+        <v>155.31</v>
       </c>
       <c r="B435" t="n">
-        <v>35858</v>
+        <v>28017</v>
       </c>
       <c r="C435" t="n">
-        <v>92.78</v>
+        <v>169.64</v>
       </c>
       <c r="D435" t="n">
-        <v>10784</v>
+        <v>29050</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>110.85</v>
+        <v>155.93</v>
       </c>
       <c r="B436" t="n">
-        <v>32229</v>
+        <v>31082</v>
       </c>
       <c r="C436" t="n">
-        <v>110.58</v>
+        <v>135.05</v>
       </c>
       <c r="D436" t="n">
-        <v>25333</v>
+        <v>27925</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>101.62</v>
+        <v>156.04</v>
       </c>
       <c r="B437" t="n">
-        <v>49159</v>
+        <v>31543</v>
       </c>
       <c r="C437" t="n">
-        <v>99.08</v>
+        <v>135.49</v>
       </c>
       <c r="D437" t="n">
-        <v>22302</v>
+        <v>12993</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>97.53</v>
+        <v>156.07</v>
       </c>
       <c r="B438" t="n">
-        <v>36133</v>
+        <v>27795</v>
       </c>
       <c r="C438" t="n">
-        <v>99.18000000000001</v>
+        <v>155.72</v>
       </c>
       <c r="D438" t="n">
-        <v>13165</v>
+        <v>20545</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>110.27</v>
+        <v>156.75</v>
       </c>
       <c r="B439" t="n">
-        <v>31273</v>
+        <v>27538</v>
       </c>
       <c r="C439" t="n">
-        <v>108.32</v>
+        <v>180</v>
       </c>
       <c r="D439" t="n">
-        <v>13781</v>
+        <v>16815</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>104.26</v>
+        <v>158.09</v>
       </c>
       <c r="B440" t="n">
-        <v>46563</v>
+        <v>32226</v>
       </c>
       <c r="C440" t="n">
-        <v>106.65</v>
+        <v>146.92</v>
       </c>
       <c r="D440" t="n">
-        <v>24113</v>
+        <v>24930</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>68.47</v>
+        <v>158.52</v>
       </c>
       <c r="B441" t="n">
-        <v>22269</v>
+        <v>30556</v>
       </c>
       <c r="C441" t="n">
-        <v>71.18000000000001</v>
+        <v>136.91</v>
       </c>
       <c r="D441" t="n">
-        <v>21176</v>
+        <v>20751</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>94.18000000000001</v>
+        <v>158.75</v>
       </c>
       <c r="B442" t="n">
-        <v>33341</v>
+        <v>28972</v>
       </c>
       <c r="C442" t="n">
-        <v>91.94</v>
+        <v>150.88</v>
       </c>
       <c r="D442" t="n">
-        <v>27298</v>
+        <v>16466</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>97.78</v>
+        <v>159.08</v>
       </c>
       <c r="B443" t="n">
-        <v>38921</v>
+        <v>33262</v>
       </c>
       <c r="C443" t="n">
-        <v>101.51</v>
+        <v>148.39</v>
       </c>
       <c r="D443" t="n">
-        <v>14010</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>94.84</v>
+        <v>159.28</v>
       </c>
       <c r="B444" t="n">
-        <v>31666</v>
+        <v>28267</v>
       </c>
       <c r="C444" t="n">
-        <v>91.12</v>
+        <v>180</v>
       </c>
       <c r="D444" t="n">
-        <v>29405</v>
+        <v>10982</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>89</v>
+        <v>159.38</v>
       </c>
       <c r="B445" t="n">
-        <v>22347</v>
+        <v>30693</v>
       </c>
       <c r="C445" t="n">
-        <v>91.06999999999999</v>
+        <v>165.35</v>
       </c>
       <c r="D445" t="n">
-        <v>11528</v>
+        <v>21497</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>92.28</v>
+        <v>159.48</v>
       </c>
       <c r="B446" t="n">
-        <v>28907</v>
+        <v>30841</v>
       </c>
       <c r="C446" t="n">
-        <v>91.45999999999999</v>
+        <v>133.44</v>
       </c>
       <c r="D446" t="n">
-        <v>27304</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>106.33</v>
+        <v>159.56</v>
       </c>
       <c r="B447" t="n">
-        <v>43010</v>
+        <v>28735</v>
       </c>
       <c r="C447" t="n">
-        <v>104.88</v>
+        <v>138.21</v>
       </c>
       <c r="D447" t="n">
-        <v>12793</v>
+        <v>26527</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>91.11</v>
+        <v>160.46</v>
       </c>
       <c r="B448" t="n">
-        <v>23653</v>
+        <v>29311</v>
       </c>
       <c r="C448" t="n">
-        <v>87.67</v>
+        <v>146.49</v>
       </c>
       <c r="D448" t="n">
-        <v>23921</v>
+        <v>29072</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>94.08</v>
+        <v>160.74</v>
       </c>
       <c r="B449" t="n">
-        <v>31852</v>
+        <v>31720</v>
       </c>
       <c r="C449" t="n">
-        <v>93.23</v>
+        <v>174.11</v>
       </c>
       <c r="D449" t="n">
-        <v>16270</v>
+        <v>17362</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>99.81</v>
+        <v>162.8</v>
       </c>
       <c r="B450" t="n">
-        <v>42094</v>
+        <v>33298</v>
       </c>
       <c r="C450" t="n">
-        <v>102.09</v>
+        <v>180</v>
       </c>
       <c r="D450" t="n">
-        <v>24906</v>
+        <v>24096</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>102.15</v>
+        <v>162.84</v>
       </c>
       <c r="B451" t="n">
-        <v>45851</v>
+        <v>30116</v>
       </c>
       <c r="C451" t="n">
-        <v>104.98</v>
+        <v>142.76</v>
       </c>
       <c r="D451" t="n">
-        <v>13311</v>
+        <v>11801</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>98.45999999999999</v>
+        <v>163.03</v>
       </c>
       <c r="B452" t="n">
-        <v>40946</v>
+        <v>28460</v>
       </c>
       <c r="C452" t="n">
-        <v>99.02</v>
+        <v>158.81</v>
       </c>
       <c r="D452" t="n">
-        <v>11999</v>
+        <v>28728</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>102.22</v>
+        <v>163.26</v>
       </c>
       <c r="B453" t="n">
-        <v>45484</v>
+        <v>30641</v>
       </c>
       <c r="C453" t="n">
-        <v>99.81</v>
+        <v>180</v>
       </c>
       <c r="D453" t="n">
-        <v>28510</v>
+        <v>16496</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>111.65</v>
+        <v>163.28</v>
       </c>
       <c r="B454" t="n">
-        <v>25962</v>
+        <v>29528</v>
       </c>
       <c r="C454" t="n">
-        <v>108.83</v>
+        <v>170.98</v>
       </c>
       <c r="D454" t="n">
-        <v>26287</v>
+        <v>19581</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>102.01</v>
+        <v>163.47</v>
       </c>
       <c r="B455" t="n">
-        <v>47517</v>
+        <v>27083</v>
       </c>
       <c r="C455" t="n">
-        <v>99.94</v>
+        <v>174.92</v>
       </c>
       <c r="D455" t="n">
-        <v>25050</v>
+        <v>11505</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>96.06</v>
+        <v>164.02</v>
       </c>
       <c r="B456" t="n">
-        <v>35711</v>
+        <v>28306</v>
       </c>
       <c r="C456" t="n">
-        <v>99.22</v>
+        <v>156.18</v>
       </c>
       <c r="D456" t="n">
-        <v>13123</v>
+        <v>24274</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>110.47</v>
+        <v>164.24</v>
       </c>
       <c r="B457" t="n">
-        <v>31887</v>
+        <v>27224</v>
       </c>
       <c r="C457" t="n">
-        <v>111.86</v>
+        <v>180</v>
       </c>
       <c r="D457" t="n">
-        <v>11897</v>
+        <v>24839</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>133.12</v>
+        <v>164.71</v>
       </c>
       <c r="B458" t="n">
-        <v>24938</v>
+        <v>28072</v>
       </c>
       <c r="C458" t="n">
-        <v>137.52</v>
+        <v>172.96</v>
       </c>
       <c r="D458" t="n">
-        <v>20644</v>
+        <v>19490</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>97.56999999999999</v>
+        <v>164.71</v>
       </c>
       <c r="B459" t="n">
-        <v>40614</v>
+        <v>26665</v>
       </c>
       <c r="C459" t="n">
-        <v>97.28</v>
+        <v>151.76</v>
       </c>
       <c r="D459" t="n">
-        <v>28100</v>
+        <v>16004</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>111.78</v>
+        <v>164.72</v>
       </c>
       <c r="B460" t="n">
-        <v>29062</v>
+        <v>28499</v>
       </c>
       <c r="C460" t="n">
-        <v>114.11</v>
+        <v>180</v>
       </c>
       <c r="D460" t="n">
-        <v>24795</v>
+        <v>17212</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>96.93000000000001</v>
+        <v>164.76</v>
       </c>
       <c r="B461" t="n">
-        <v>36404</v>
+        <v>26927</v>
       </c>
       <c r="C461" t="n">
-        <v>97.29000000000001</v>
+        <v>180</v>
       </c>
       <c r="D461" t="n">
-        <v>11540</v>
+        <v>11313</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>98.44</v>
+        <v>165.4</v>
       </c>
       <c r="B462" t="n">
-        <v>41197</v>
+        <v>27152</v>
       </c>
       <c r="C462" t="n">
-        <v>94.47</v>
+        <v>180</v>
       </c>
       <c r="D462" t="n">
-        <v>10623</v>
+        <v>29003</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>93.11</v>
+        <v>165.41</v>
       </c>
       <c r="B463" t="n">
-        <v>31137</v>
+        <v>28530</v>
       </c>
       <c r="C463" t="n">
-        <v>92.98</v>
+        <v>143.61</v>
       </c>
       <c r="D463" t="n">
-        <v>16045</v>
+        <v>10175</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>76.37</v>
+        <v>165.45</v>
       </c>
       <c r="B464" t="n">
-        <v>19484</v>
+        <v>28874</v>
       </c>
       <c r="C464" t="n">
-        <v>75.42</v>
+        <v>178.69</v>
       </c>
       <c r="D464" t="n">
-        <v>17575</v>
+        <v>10948</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>112.69</v>
+        <v>165.47</v>
       </c>
       <c r="B465" t="n">
-        <v>25806</v>
+        <v>27249</v>
       </c>
       <c r="C465" t="n">
-        <v>116.45</v>
+        <v>132.75</v>
       </c>
       <c r="D465" t="n">
-        <v>24860</v>
+        <v>13336</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>111.97</v>
+        <v>166.08</v>
       </c>
       <c r="B466" t="n">
-        <v>27508</v>
+        <v>27099</v>
       </c>
       <c r="C466" t="n">
-        <v>113.17</v>
+        <v>175.4</v>
       </c>
       <c r="D466" t="n">
-        <v>16108</v>
+        <v>11692</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>118.32</v>
+        <v>167.03</v>
       </c>
       <c r="B467" t="n">
-        <v>21893</v>
+        <v>25923</v>
       </c>
       <c r="C467" t="n">
-        <v>122.3</v>
+        <v>158.24</v>
       </c>
       <c r="D467" t="n">
-        <v>18114</v>
+        <v>22828</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>104.91</v>
+        <v>167.1</v>
       </c>
       <c r="B468" t="n">
-        <v>43950</v>
+        <v>25122</v>
       </c>
       <c r="C468" t="n">
-        <v>107.68</v>
+        <v>174.93</v>
       </c>
       <c r="D468" t="n">
-        <v>19944</v>
+        <v>21218</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>96.95</v>
+        <v>167.4</v>
       </c>
       <c r="B469" t="n">
-        <v>36518</v>
+        <v>26086</v>
       </c>
       <c r="C469" t="n">
-        <v>95.45</v>
+        <v>180</v>
       </c>
       <c r="D469" t="n">
-        <v>14889</v>
+        <v>24200</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>106.49</v>
+        <v>167.49</v>
       </c>
       <c r="B470" t="n">
-        <v>41268</v>
+        <v>26649</v>
       </c>
       <c r="C470" t="n">
-        <v>107.85</v>
+        <v>170.13</v>
       </c>
       <c r="D470" t="n">
-        <v>25756</v>
+        <v>29344</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>107.75</v>
+        <v>167.68</v>
       </c>
       <c r="B471" t="n">
-        <v>39206</v>
+        <v>25822</v>
       </c>
       <c r="C471" t="n">
-        <v>103.08</v>
+        <v>180</v>
       </c>
       <c r="D471" t="n">
-        <v>11401</v>
+        <v>21740</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>90.45</v>
+        <v>168.26</v>
       </c>
       <c r="B472" t="n">
-        <v>22816</v>
+        <v>24038</v>
       </c>
       <c r="C472" t="n">
-        <v>90.3</v>
+        <v>174.14</v>
       </c>
       <c r="D472" t="n">
-        <v>17714</v>
+        <v>16278</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>110.5</v>
+        <v>168.41</v>
       </c>
       <c r="B473" t="n">
-        <v>31390</v>
+        <v>24578</v>
       </c>
       <c r="C473" t="n">
-        <v>109.48</v>
+        <v>175.68</v>
       </c>
       <c r="D473" t="n">
-        <v>10405</v>
+        <v>20896</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>92.87</v>
+        <v>169.53</v>
       </c>
       <c r="B474" t="n">
-        <v>27826</v>
+        <v>23300</v>
       </c>
       <c r="C474" t="n">
-        <v>92.25</v>
+        <v>180</v>
       </c>
       <c r="D474" t="n">
-        <v>12468</v>
+        <v>15651</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>112.76</v>
+        <v>169.57</v>
       </c>
       <c r="B475" t="n">
-        <v>26456</v>
+        <v>23347</v>
       </c>
       <c r="C475" t="n">
-        <v>113.7</v>
+        <v>180</v>
       </c>
       <c r="D475" t="n">
-        <v>19145</v>
+        <v>15111</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>111.04</v>
+        <v>170.51</v>
       </c>
       <c r="B476" t="n">
-        <v>29808</v>
+        <v>23586</v>
       </c>
       <c r="C476" t="n">
-        <v>115.69</v>
+        <v>175.05</v>
       </c>
       <c r="D476" t="n">
-        <v>13583</v>
+        <v>21474</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>63.4</v>
+        <v>170.63</v>
       </c>
       <c r="B477" t="n">
-        <v>24080</v>
+        <v>25552</v>
       </c>
       <c r="C477" t="n">
-        <v>63.31</v>
+        <v>180</v>
       </c>
       <c r="D477" t="n">
-        <v>29536</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>97.51000000000001</v>
+        <v>171.64</v>
       </c>
       <c r="B478" t="n">
-        <v>42658</v>
+        <v>22141</v>
       </c>
       <c r="C478" t="n">
-        <v>98.15000000000001</v>
+        <v>138.76</v>
       </c>
       <c r="D478" t="n">
-        <v>12125</v>
+        <v>12136</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>102.42</v>
+        <v>172.74</v>
       </c>
       <c r="B479" t="n">
-        <v>43707</v>
+        <v>20540</v>
       </c>
       <c r="C479" t="n">
-        <v>106.07</v>
+        <v>175.83</v>
       </c>
       <c r="D479" t="n">
-        <v>24920</v>
+        <v>15507</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>104.69</v>
+        <v>172.85</v>
       </c>
       <c r="B480" t="n">
-        <v>46406</v>
+        <v>19473</v>
       </c>
       <c r="C480" t="n">
-        <v>104.9</v>
+        <v>180</v>
       </c>
       <c r="D480" t="n">
-        <v>16527</v>
+        <v>19604</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>149.82</v>
+        <v>173.09</v>
       </c>
       <c r="B481" t="n">
-        <v>24837</v>
+        <v>21075</v>
       </c>
       <c r="C481" t="n">
-        <v>150.39</v>
+        <v>180</v>
       </c>
       <c r="D481" t="n">
-        <v>22478</v>
+        <v>12501</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>103.13</v>
+        <v>174.14</v>
       </c>
       <c r="B482" t="n">
-        <v>48819</v>
+        <v>18889</v>
       </c>
       <c r="C482" t="n">
-        <v>105.96</v>
+        <v>180</v>
       </c>
       <c r="D482" t="n">
-        <v>29677</v>
+        <v>16963</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>43.18</v>
+        <v>174.21</v>
       </c>
       <c r="B483" t="n">
-        <v>23655</v>
+        <v>20314</v>
       </c>
       <c r="C483" t="n">
-        <v>43.09</v>
+        <v>172.75</v>
       </c>
       <c r="D483" t="n">
-        <v>11919</v>
+        <v>15377</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>98.62</v>
+        <v>174.26</v>
       </c>
       <c r="B484" t="n">
-        <v>41161</v>
+        <v>18936</v>
       </c>
       <c r="C484" t="n">
-        <v>99.72</v>
+        <v>178.87</v>
       </c>
       <c r="D484" t="n">
-        <v>23097</v>
+        <v>29035</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>113.52</v>
+        <v>174.76</v>
       </c>
       <c r="B485" t="n">
-        <v>25142</v>
+        <v>20866</v>
       </c>
       <c r="C485" t="n">
-        <v>115.74</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>13376</v>
+        <v>15233</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>104.82</v>
+        <v>175.11</v>
       </c>
       <c r="B486" t="n">
-        <v>47257</v>
+        <v>21076</v>
       </c>
       <c r="C486" t="n">
-        <v>108.36</v>
+        <v>165.66</v>
       </c>
       <c r="D486" t="n">
-        <v>16440</v>
+        <v>22220</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>109.51</v>
+        <v>175.42</v>
       </c>
       <c r="B487" t="n">
-        <v>33712</v>
+        <v>19948</v>
       </c>
       <c r="C487" t="n">
-        <v>110.51</v>
+        <v>172.26</v>
       </c>
       <c r="D487" t="n">
-        <v>22884</v>
+        <v>18082</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>49.78</v>
+        <v>175.71</v>
       </c>
       <c r="B488" t="n">
-        <v>24183</v>
+        <v>20853</v>
       </c>
       <c r="C488" t="n">
-        <v>51.94</v>
+        <v>146.94</v>
       </c>
       <c r="D488" t="n">
-        <v>14684</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>98.56999999999999</v>
+        <v>175.83</v>
       </c>
       <c r="B489" t="n">
-        <v>41690</v>
+        <v>19854</v>
       </c>
       <c r="C489" t="n">
-        <v>101.38</v>
+        <v>180</v>
       </c>
       <c r="D489" t="n">
-        <v>29384</v>
+        <v>14502</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>93.92</v>
+        <v>175.98</v>
       </c>
       <c r="B490" t="n">
-        <v>32951</v>
+        <v>16498</v>
       </c>
       <c r="C490" t="n">
-        <v>93.73</v>
+        <v>149.17</v>
       </c>
       <c r="D490" t="n">
-        <v>20934</v>
+        <v>29911</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>98.15000000000001</v>
+        <v>176.43</v>
       </c>
       <c r="B491" t="n">
-        <v>40650</v>
+        <v>18409</v>
       </c>
       <c r="C491" t="n">
-        <v>98.97</v>
+        <v>132.47</v>
       </c>
       <c r="D491" t="n">
-        <v>21341</v>
+        <v>27784</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>106.87</v>
+        <v>176.49</v>
       </c>
       <c r="B492" t="n">
-        <v>41475</v>
+        <v>17765</v>
       </c>
       <c r="C492" t="n">
-        <v>102.66</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>12189</v>
+        <v>25857</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>158.69</v>
+        <v>176.68</v>
       </c>
       <c r="B493" t="n">
-        <v>21385</v>
+        <v>19428</v>
       </c>
       <c r="C493" t="n">
-        <v>153.81</v>
+        <v>145.61</v>
       </c>
       <c r="D493" t="n">
-        <v>11644</v>
+        <v>22261</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>158.13</v>
+        <v>176.77</v>
       </c>
       <c r="B494" t="n">
-        <v>24677</v>
+        <v>19820</v>
       </c>
       <c r="C494" t="n">
-        <v>158.95</v>
+        <v>154.67</v>
       </c>
       <c r="D494" t="n">
-        <v>17201</v>
+        <v>14383</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>44.33</v>
+        <v>176.77</v>
       </c>
       <c r="B495" t="n">
-        <v>20413</v>
+        <v>19108</v>
       </c>
       <c r="C495" t="n">
-        <v>45.21</v>
+        <v>177.83</v>
       </c>
       <c r="D495" t="n">
-        <v>15596</v>
+        <v>14792</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>102.31</v>
+        <v>176.82</v>
       </c>
       <c r="B496" t="n">
-        <v>46205</v>
+        <v>19248</v>
       </c>
       <c r="C496" t="n">
-        <v>104.08</v>
+        <v>180</v>
       </c>
       <c r="D496" t="n">
-        <v>18566</v>
+        <v>28574</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>113.31</v>
+        <v>177.38</v>
       </c>
       <c r="B497" t="n">
-        <v>26281</v>
+        <v>19577</v>
       </c>
       <c r="C497" t="n">
-        <v>111.34</v>
+        <v>180</v>
       </c>
       <c r="D497" t="n">
-        <v>23208</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>90.52</v>
+        <v>177.52</v>
       </c>
       <c r="B498" t="n">
-        <v>22724</v>
+        <v>18434</v>
       </c>
       <c r="C498" t="n">
-        <v>93.31</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>23482</v>
+        <v>26638</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>108.76</v>
+        <v>178.05</v>
       </c>
       <c r="B499" t="n">
-        <v>37197</v>
+        <v>18617</v>
       </c>
       <c r="C499" t="n">
-        <v>105.04</v>
+        <v>180</v>
       </c>
       <c r="D499" t="n">
-        <v>26954</v>
+        <v>17534</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>113.4</v>
+        <v>178.06</v>
       </c>
       <c r="B500" t="n">
-        <v>24182</v>
+        <v>20892</v>
       </c>
       <c r="C500" t="n">
-        <v>110.5</v>
+        <v>177.31</v>
       </c>
       <c r="D500" t="n">
-        <v>13596</v>
+        <v>13891</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>91.95999999999999</v>
+        <v>179.07</v>
       </c>
       <c r="B501" t="n">
-        <v>27753</v>
+        <v>17772</v>
       </c>
       <c r="C501" t="n">
-        <v>94.09999999999999</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>10165</v>
+        <v>11351</v>
       </c>
     </row>
   </sheetData>
